--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/raimondo_reggio_ifabfoundation_org/Documents/Desktop/GitHub/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_30E9E6B1175D780E62355476585DCE3A8741F18A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E602B83D-0377-4A3E-B84C-E1D76A9CB024}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_7D917707D474AA0E62355476585DCE3A8743D975" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2389093E-9595-4B32-8DF4-74FDB9F937A7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4080" yWindow="-17715" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -94,6 +107,9 @@
     <t>7125.0, 2.0</t>
   </si>
   <si>
+    <t>Cohort</t>
+  </si>
+  <si>
     <t>COLPROT</t>
   </si>
   <si>
@@ -409,9 +425,6 @@
     <t>ADNI3, ADNI4</t>
   </si>
   <si>
-    <t>Cohort</t>
-  </si>
-  <si>
     <t>PHASE</t>
   </si>
   <si>
@@ -1609,72 +1622,72 @@
     <t>186866.0, 2.0</t>
   </si>
   <si>
+    <t>Participant Demographic Information</t>
+  </si>
+  <si>
+    <t>PTDEMOG</t>
+  </si>
+  <si>
+    <t>011_S_0002, 022_S_0001, 011_S_0003, 022_S_0004, 011_S_0005</t>
+  </si>
+  <si>
+    <t>10816.0, 1.0</t>
+  </si>
+  <si>
+    <t>sc, f, m06, bl, m12</t>
+  </si>
+  <si>
+    <t>VISDATE</t>
+  </si>
+  <si>
+    <t>2005-08-17, 2005-08-18, 2005-08-23, 2005-08-25, 2005-08-26</t>
+  </si>
+  <si>
+    <t>1.0, 2.0, -4.0, nan</t>
+  </si>
+  <si>
+    <t>2.0, -4.0</t>
+  </si>
+  <si>
+    <t>PTDOB</t>
+  </si>
+  <si>
+    <t>04/1931, 12/1944, 05/1924, 01/1938, 12/1931</t>
+  </si>
+  <si>
+    <t>1.0, 2.0, 3.0, 4.0, 5.0, -4.0, nan, 6.0</t>
+  </si>
+  <si>
+    <t>6.0, -4.0</t>
+  </si>
+  <si>
+    <t>20.0, -4.0</t>
+  </si>
+  <si>
+    <t>PTADBEG</t>
+  </si>
+  <si>
+    <t>2010.0, -4.0</t>
+  </si>
+  <si>
+    <t>2.0, -4.0, 1.0, 3.0, nan</t>
+  </si>
+  <si>
+    <t>5, -4, 6, 4, 2</t>
+  </si>
+  <si>
+    <t>186128.0, 12.0</t>
+  </si>
+  <si>
+    <t>Participant Demographics</t>
+  </si>
+  <si>
     <t>GO</t>
   </si>
   <si>
     <t>VISCODE2</t>
   </si>
   <si>
-    <t>Participant Demographic Information</t>
-  </si>
-  <si>
-    <t>PTDEMOG</t>
-  </si>
-  <si>
-    <t>011_S_0002, 022_S_0001, 011_S_0003, 022_S_0004, 011_S_0005</t>
-  </si>
-  <si>
-    <t>10816.0, 1.0</t>
-  </si>
-  <si>
-    <t>sc, f, m06, bl, m12</t>
-  </si>
-  <si>
-    <t>VISDATE</t>
-  </si>
-  <si>
-    <t>2005-08-17, 2005-08-18, 2005-08-23, 2005-08-25, 2005-08-26</t>
-  </si>
-  <si>
-    <t>1.0, 2.0, -4.0, nan</t>
-  </si>
-  <si>
-    <t>2.0, -4.0</t>
-  </si>
-  <si>
-    <t>PTDOB</t>
-  </si>
-  <si>
-    <t>04/1931, 12/1944, 05/1924, 01/1938, 12/1931</t>
-  </si>
-  <si>
-    <t>1.0, 2.0, 3.0, 4.0, 5.0, -4.0, nan, 6.0</t>
-  </si>
-  <si>
-    <t>6.0, -4.0</t>
-  </si>
-  <si>
-    <t>20.0, -4.0</t>
-  </si>
-  <si>
-    <t>PTADBEG</t>
-  </si>
-  <si>
-    <t>2010.0, -4.0</t>
-  </si>
-  <si>
-    <t>2.0, -4.0, 1.0, 3.0, nan</t>
-  </si>
-  <si>
-    <t>5, -4, 6, 4, 2</t>
-  </si>
-  <si>
-    <t>186128.0, 12.0</t>
-  </si>
-  <si>
-    <t>Participant Demographics</t>
-  </si>
-  <si>
     <t>PTDOBYY</t>
   </si>
   <si>
@@ -1900,25 +1913,25 @@
     <t>186867.0, 2.0</t>
   </si>
   <si>
+    <t>DXDSEV</t>
+  </si>
+  <si>
+    <t>DXDDUE</t>
+  </si>
+  <si>
+    <t>nan, 1.0, 2.0</t>
+  </si>
+  <si>
+    <t>DXDEP</t>
+  </si>
+  <si>
+    <t>nan, 0.0, 1.0</t>
+  </si>
+  <si>
+    <t>1.0, 0.0</t>
+  </si>
+  <si>
     <t>DXCHANGE</t>
-  </si>
-  <si>
-    <t>DXDSEV</t>
-  </si>
-  <si>
-    <t>DXDDUE</t>
-  </si>
-  <si>
-    <t>nan, 1.0, 2.0</t>
-  </si>
-  <si>
-    <t>DXDEP</t>
-  </si>
-  <si>
-    <t>nan, 0.0, 1.0</t>
-  </si>
-  <si>
-    <t>1.0, 0.0</t>
   </si>
   <si>
     <t>DIAGNOSIS</t>
@@ -1937,7 +1950,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1949,14 +1962,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1994,12 +1999,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2311,8 +2315,8 @@
     <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="71.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="67.5546875" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.5546875" bestFit="1" customWidth="1"/>
@@ -2441,19 +2445,19 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
@@ -2478,20 +2482,20 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
+      <c r="C5" t="s">
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
@@ -2517,19 +2521,19 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -2555,22 +2559,22 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
         <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7">
         <v>16412</v>
@@ -2593,19 +2597,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>19</v>
@@ -2631,13 +2635,13 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -2646,7 +2650,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I9">
         <v>16421</v>
@@ -2669,19 +2673,19 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>19</v>
@@ -2707,19 +2711,19 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -2745,19 +2749,19 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
         <v>19</v>
@@ -2783,22 +2787,22 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13">
         <v>16056</v>
@@ -2821,22 +2825,22 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I14">
         <v>223</v>
@@ -2845,7 +2849,7 @@
         <v>16198</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -2859,22 +2863,22 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I15">
         <v>3080</v>
@@ -2883,7 +2887,7 @@
         <v>13341</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -2897,22 +2901,22 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16">
         <v>11747</v>
@@ -2935,22 +2939,22 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17">
         <v>11431</v>
@@ -2973,22 +2977,22 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
         <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I18">
         <v>11330</v>
@@ -3011,22 +3015,22 @@
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
         <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19">
         <v>11469</v>
@@ -3049,22 +3053,22 @@
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20">
         <v>11346</v>
@@ -3087,22 +3091,22 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I21">
         <v>11743</v>
@@ -3125,22 +3129,22 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
         <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I22">
         <v>7426</v>
@@ -3149,7 +3153,7 @@
         <v>8995</v>
       </c>
       <c r="K22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -3163,22 +3167,22 @@
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23">
         <v>9468</v>
@@ -3201,22 +3205,22 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24">
         <v>8853</v>
@@ -3239,22 +3243,22 @@
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I25">
         <v>8440</v>
@@ -3277,22 +3281,22 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I26">
         <v>8440</v>
@@ -3315,22 +3319,22 @@
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27">
         <v>8440</v>
@@ -3353,22 +3357,22 @@
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I28">
         <v>10115</v>
@@ -3391,19 +3395,19 @@
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
         <v>19</v>
@@ -3429,19 +3433,19 @@
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
@@ -3467,19 +3471,19 @@
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H31" t="s">
         <v>19</v>
@@ -3505,22 +3509,22 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
         <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32">
         <v>16421</v>
@@ -3543,22 +3547,22 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G33" t="s">
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I33">
         <v>16381</v>
@@ -3581,22 +3585,22 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G34" t="s">
         <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I34">
         <v>16309</v>
@@ -3619,22 +3623,22 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G35" t="s">
         <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I35">
         <v>16419</v>
@@ -3657,22 +3661,22 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G36" t="s">
         <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I36">
         <v>16380</v>
@@ -3695,22 +3699,22 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G37" t="s">
         <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I37">
         <v>16335</v>
@@ -3733,22 +3737,22 @@
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G38" t="s">
         <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38">
         <v>15643</v>
@@ -3771,22 +3775,22 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G39" t="s">
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I39">
         <v>14272</v>
@@ -3809,22 +3813,22 @@
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G40" t="s">
         <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I40">
         <v>15945</v>
@@ -3847,22 +3851,22 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G41" t="s">
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I41">
         <v>14111</v>
@@ -3885,22 +3889,22 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I42">
         <v>14111</v>
@@ -3923,22 +3927,22 @@
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G43" t="s">
         <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I43">
         <v>14111</v>
@@ -3961,22 +3965,22 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G44" t="s">
         <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I44">
         <v>16158</v>
@@ -3999,22 +4003,22 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G45" t="s">
         <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I45">
         <v>8998</v>
@@ -4023,7 +4027,7 @@
         <v>7423</v>
       </c>
       <c r="K45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -4031,16 +4035,16 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
@@ -4052,7 +4056,7 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I46">
         <v>1247</v>
@@ -4061,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -4069,13 +4073,13 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
         <v>130</v>
@@ -4096,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -4104,19 +4108,19 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
@@ -4134,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -4142,16 +4146,16 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E49" t="s">
         <v>133</v>
@@ -4163,7 +4167,7 @@
         <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I49">
         <v>1247</v>
@@ -4172,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -4180,22 +4184,22 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E50" t="s">
         <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
         <v>135</v>
@@ -4210,7 +4214,7 @@
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -4218,16 +4222,16 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
         <v>137</v>
@@ -4248,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -4256,16 +4260,16 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
         <v>140</v>
@@ -4286,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -4294,22 +4298,22 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
         <v>142</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E53" t="s">
         <v>143</v>
       </c>
       <c r="F53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G53" t="s">
         <v>19</v>
@@ -4324,7 +4328,7 @@
         <v>33</v>
       </c>
       <c r="K53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -4332,22 +4336,22 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E54" t="s">
         <v>145</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" t="s">
         <v>19</v>
@@ -4362,7 +4366,7 @@
         <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -4370,90 +4374,90 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
         <v>142</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E59" t="s">
         <v>147</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G59" t="s">
         <v>19</v>
@@ -4468,7 +4472,7 @@
         <v>7</v>
       </c>
       <c r="K59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -4476,16 +4480,16 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E60" t="s">
         <v>149</v>
@@ -4493,22 +4497,22 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E61" t="s">
         <v>150</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G61" t="s">
         <v>151</v>
@@ -4523,7 +4527,7 @@
         <v>2</v>
       </c>
       <c r="K61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -4531,22 +4535,22 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
         <v>153</v>
       </c>
       <c r="F62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G62" t="s">
         <v>19</v>
@@ -4561,7 +4565,7 @@
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -4569,16 +4573,16 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E63" t="s">
         <v>155</v>
@@ -4595,7 +4599,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
         <v>21</v>
@@ -4609,13 +4613,13 @@
         <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -4626,10 +4630,10 @@
         <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E66" t="s">
         <v>158</v>
@@ -4643,10 +4647,10 @@
         <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E67" t="s">
         <v>159</v>
@@ -4660,10 +4664,10 @@
         <v>157</v>
       </c>
       <c r="C68" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E68" t="s">
         <v>160</v>
@@ -4677,10 +4681,10 @@
         <v>157</v>
       </c>
       <c r="C69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D69" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E69" t="s">
         <v>161</v>
@@ -4697,7 +4701,7 @@
         <v>162</v>
       </c>
       <c r="D70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E70" t="s">
         <v>163</v>
@@ -4711,10 +4715,10 @@
         <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E71" t="s">
         <v>164</v>
@@ -4728,10 +4732,10 @@
         <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D72" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E72" t="s">
         <v>165</v>
@@ -4745,10 +4749,10 @@
         <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E73" t="s">
         <v>166</v>
@@ -4765,7 +4769,7 @@
         <v>162</v>
       </c>
       <c r="D74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
         <v>167</v>
@@ -4779,10 +4783,10 @@
         <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
         <v>168</v>
@@ -4796,10 +4800,10 @@
         <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s">
         <v>169</v>
@@ -4813,10 +4817,10 @@
         <v>157</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E77" t="s">
         <v>170</v>
@@ -4833,7 +4837,7 @@
         <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E78" t="s">
         <v>171</v>
@@ -4850,7 +4854,7 @@
         <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E79" t="s">
         <v>172</v>
@@ -4864,10 +4868,10 @@
         <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E80" t="s">
         <v>173</v>
@@ -4881,10 +4885,10 @@
         <v>157</v>
       </c>
       <c r="C81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E81" t="s">
         <v>174</v>
@@ -4898,10 +4902,10 @@
         <v>157</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E82" t="s">
         <v>175</v>
@@ -4915,10 +4919,10 @@
         <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E83" t="s">
         <v>176</v>
@@ -4932,10 +4936,10 @@
         <v>157</v>
       </c>
       <c r="C84" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E84" t="s">
         <v>177</v>
@@ -4949,10 +4953,10 @@
         <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E85" t="s">
         <v>178</v>
@@ -4966,10 +4970,10 @@
         <v>157</v>
       </c>
       <c r="C86" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D86" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E86" t="s">
         <v>179</v>
@@ -4983,10 +4987,10 @@
         <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E87" t="s">
         <v>180</v>
@@ -5000,10 +5004,10 @@
         <v>157</v>
       </c>
       <c r="C88" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D88" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E88" t="s">
         <v>181</v>
@@ -5017,10 +5021,10 @@
         <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E89" t="s">
         <v>182</v>
@@ -5034,10 +5038,10 @@
         <v>157</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E90" t="s">
         <v>183</v>
@@ -5051,10 +5055,10 @@
         <v>157</v>
       </c>
       <c r="C91" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D91" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E91" t="s">
         <v>184</v>
@@ -5068,10 +5072,10 @@
         <v>157</v>
       </c>
       <c r="C92" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E92" t="s">
         <v>185</v>
@@ -5085,10 +5089,10 @@
         <v>157</v>
       </c>
       <c r="C93" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D93" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E93" t="s">
         <v>186</v>
@@ -5102,10 +5106,10 @@
         <v>157</v>
       </c>
       <c r="C94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E94" t="s">
         <v>187</v>
@@ -5119,10 +5123,10 @@
         <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E95" t="s">
         <v>188</v>
@@ -5136,10 +5140,10 @@
         <v>157</v>
       </c>
       <c r="C96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D96" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E96" t="s">
         <v>189</v>
@@ -5153,10 +5157,10 @@
         <v>157</v>
       </c>
       <c r="C97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E97" t="s">
         <v>190</v>
@@ -5170,10 +5174,10 @@
         <v>157</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E98" t="s">
         <v>191</v>
@@ -5190,7 +5194,7 @@
         <v>162</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E99" t="s">
         <v>192</v>
@@ -5204,10 +5208,10 @@
         <v>157</v>
       </c>
       <c r="C100" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E100" t="s">
         <v>193</v>
@@ -5221,10 +5225,10 @@
         <v>157</v>
       </c>
       <c r="C101" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D101" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E101" t="s">
         <v>194</v>
@@ -5238,10 +5242,10 @@
         <v>157</v>
       </c>
       <c r="C102" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D102" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E102" t="s">
         <v>195</v>
@@ -5255,10 +5259,10 @@
         <v>157</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E103" t="s">
         <v>196</v>
@@ -5272,10 +5276,10 @@
         <v>157</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D104" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E104" t="s">
         <v>197</v>
@@ -5289,10 +5293,10 @@
         <v>157</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E105" t="s">
         <v>198</v>
@@ -5306,10 +5310,10 @@
         <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E106" t="s">
         <v>199</v>
@@ -5323,10 +5327,10 @@
         <v>157</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E107" t="s">
         <v>200</v>
@@ -5378,7 +5382,7 @@
         <v>202</v>
       </c>
       <c r="C109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -5395,7 +5399,7 @@
         <v>202</v>
       </c>
       <c r="C110" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
@@ -5429,7 +5433,7 @@
         <v>202</v>
       </c>
       <c r="C112" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
@@ -6160,7 +6164,7 @@
         <v>202</v>
       </c>
       <c r="C155" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s">
         <v>15</v>
@@ -6449,7 +6453,7 @@
         <v>202</v>
       </c>
       <c r="C172" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D172" t="s">
         <v>15</v>
@@ -6466,7 +6470,7 @@
         <v>202</v>
       </c>
       <c r="C173" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D173" t="s">
         <v>15</v>
@@ -6483,7 +6487,7 @@
         <v>202</v>
       </c>
       <c r="C174" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D174" t="s">
         <v>15</v>
@@ -6534,7 +6538,7 @@
         <v>202</v>
       </c>
       <c r="C177" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D177" t="s">
         <v>15</v>
@@ -6551,7 +6555,7 @@
         <v>202</v>
       </c>
       <c r="C178" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D178" t="s">
         <v>15</v>
@@ -6653,7 +6657,7 @@
         <v>202</v>
       </c>
       <c r="C184" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D184" t="s">
         <v>15</v>
@@ -6670,7 +6674,7 @@
         <v>202</v>
       </c>
       <c r="C185" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D185" t="s">
         <v>15</v>
@@ -6687,7 +6691,7 @@
         <v>202</v>
       </c>
       <c r="C186" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D186" t="s">
         <v>15</v>
@@ -6823,7 +6827,7 @@
         <v>202</v>
       </c>
       <c r="C194" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D194" t="s">
         <v>15</v>
@@ -6840,7 +6844,7 @@
         <v>202</v>
       </c>
       <c r="C195" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
@@ -6857,7 +6861,7 @@
         <v>202</v>
       </c>
       <c r="C196" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D196" t="s">
         <v>15</v>
@@ -6993,7 +6997,7 @@
         <v>202</v>
       </c>
       <c r="C204" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D204" t="s">
         <v>15</v>
@@ -7010,7 +7014,7 @@
         <v>202</v>
       </c>
       <c r="C205" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D205" t="s">
         <v>15</v>
@@ -7027,7 +7031,7 @@
         <v>202</v>
       </c>
       <c r="C206" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D206" t="s">
         <v>15</v>
@@ -7163,7 +7167,7 @@
         <v>202</v>
       </c>
       <c r="C214" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D214" t="s">
         <v>15</v>
@@ -7180,7 +7184,7 @@
         <v>202</v>
       </c>
       <c r="C215" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D215" t="s">
         <v>15</v>
@@ -7197,7 +7201,7 @@
         <v>202</v>
       </c>
       <c r="C216" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D216" t="s">
         <v>15</v>
@@ -7333,7 +7337,7 @@
         <v>202</v>
       </c>
       <c r="C224" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -7350,7 +7354,7 @@
         <v>202</v>
       </c>
       <c r="C225" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -7367,7 +7371,7 @@
         <v>202</v>
       </c>
       <c r="C226" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D226" t="s">
         <v>15</v>
@@ -7503,7 +7507,7 @@
         <v>202</v>
       </c>
       <c r="C234" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D234" t="s">
         <v>15</v>
@@ -7520,7 +7524,7 @@
         <v>202</v>
       </c>
       <c r="C235" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D235" t="s">
         <v>15</v>
@@ -7537,7 +7541,7 @@
         <v>202</v>
       </c>
       <c r="C236" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D236" t="s">
         <v>15</v>
@@ -7673,7 +7677,7 @@
         <v>202</v>
       </c>
       <c r="C244" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D244" t="s">
         <v>15</v>
@@ -7690,7 +7694,7 @@
         <v>202</v>
       </c>
       <c r="C245" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D245" t="s">
         <v>15</v>
@@ -7707,7 +7711,7 @@
         <v>202</v>
       </c>
       <c r="C246" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D246" t="s">
         <v>15</v>
@@ -7843,7 +7847,7 @@
         <v>202</v>
       </c>
       <c r="C254" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
@@ -7860,7 +7864,7 @@
         <v>202</v>
       </c>
       <c r="C255" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D255" t="s">
         <v>15</v>
@@ -7877,7 +7881,7 @@
         <v>202</v>
       </c>
       <c r="C256" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D256" t="s">
         <v>15</v>
@@ -8013,7 +8017,7 @@
         <v>202</v>
       </c>
       <c r="C264" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D264" t="s">
         <v>15</v>
@@ -8030,7 +8034,7 @@
         <v>202</v>
       </c>
       <c r="C265" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D265" t="s">
         <v>15</v>
@@ -8047,7 +8051,7 @@
         <v>202</v>
       </c>
       <c r="C266" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D266" t="s">
         <v>15</v>
@@ -8183,7 +8187,7 @@
         <v>202</v>
       </c>
       <c r="C274" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D274" t="s">
         <v>15</v>
@@ -8200,7 +8204,7 @@
         <v>202</v>
       </c>
       <c r="C275" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D275" t="s">
         <v>15</v>
@@ -8217,7 +8221,7 @@
         <v>202</v>
       </c>
       <c r="C276" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D276" t="s">
         <v>15</v>
@@ -8353,7 +8357,7 @@
         <v>202</v>
       </c>
       <c r="C284" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D284" t="s">
         <v>15</v>
@@ -8370,7 +8374,7 @@
         <v>202</v>
       </c>
       <c r="C285" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D285" t="s">
         <v>15</v>
@@ -8387,7 +8391,7 @@
         <v>202</v>
       </c>
       <c r="C286" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D286" t="s">
         <v>15</v>
@@ -8523,7 +8527,7 @@
         <v>202</v>
       </c>
       <c r="C294" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D294" t="s">
         <v>15</v>
@@ -8540,7 +8544,7 @@
         <v>202</v>
       </c>
       <c r="C295" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D295" t="s">
         <v>15</v>
@@ -8557,7 +8561,7 @@
         <v>202</v>
       </c>
       <c r="C296" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D296" t="s">
         <v>15</v>
@@ -8693,7 +8697,7 @@
         <v>202</v>
       </c>
       <c r="C304" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D304" t="s">
         <v>15</v>
@@ -8710,7 +8714,7 @@
         <v>202</v>
       </c>
       <c r="C305" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D305" t="s">
         <v>15</v>
@@ -8727,7 +8731,7 @@
         <v>202</v>
       </c>
       <c r="C306" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D306" t="s">
         <v>15</v>
@@ -8863,7 +8867,7 @@
         <v>202</v>
       </c>
       <c r="C314" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D314" t="s">
         <v>15</v>
@@ -8880,7 +8884,7 @@
         <v>202</v>
       </c>
       <c r="C315" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D315" t="s">
         <v>15</v>
@@ -8897,7 +8901,7 @@
         <v>202</v>
       </c>
       <c r="C316" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D316" t="s">
         <v>15</v>
@@ -9033,7 +9037,7 @@
         <v>202</v>
       </c>
       <c r="C324" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D324" t="s">
         <v>15</v>
@@ -9050,7 +9054,7 @@
         <v>202</v>
       </c>
       <c r="C325" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D325" t="s">
         <v>15</v>
@@ -9067,7 +9071,7 @@
         <v>202</v>
       </c>
       <c r="C326" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D326" t="s">
         <v>15</v>
@@ -9203,7 +9207,7 @@
         <v>202</v>
       </c>
       <c r="C334" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D334" t="s">
         <v>15</v>
@@ -9220,7 +9224,7 @@
         <v>202</v>
       </c>
       <c r="C335" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D335" t="s">
         <v>15</v>
@@ -9237,7 +9241,7 @@
         <v>202</v>
       </c>
       <c r="C336" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D336" t="s">
         <v>15</v>
@@ -9373,7 +9377,7 @@
         <v>202</v>
       </c>
       <c r="C344" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D344" t="s">
         <v>15</v>
@@ -9390,7 +9394,7 @@
         <v>202</v>
       </c>
       <c r="C345" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D345" t="s">
         <v>15</v>
@@ -9407,7 +9411,7 @@
         <v>202</v>
       </c>
       <c r="C346" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D346" t="s">
         <v>15</v>
@@ -9543,7 +9547,7 @@
         <v>202</v>
       </c>
       <c r="C354" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D354" t="s">
         <v>15</v>
@@ -9560,7 +9564,7 @@
         <v>202</v>
       </c>
       <c r="C355" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D355" t="s">
         <v>15</v>
@@ -9577,7 +9581,7 @@
         <v>202</v>
       </c>
       <c r="C356" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D356" t="s">
         <v>15</v>
@@ -9713,7 +9717,7 @@
         <v>202</v>
       </c>
       <c r="C364" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D364" t="s">
         <v>15</v>
@@ -9730,7 +9734,7 @@
         <v>202</v>
       </c>
       <c r="C365" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D365" t="s">
         <v>15</v>
@@ -9747,7 +9751,7 @@
         <v>202</v>
       </c>
       <c r="C366" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D366" t="s">
         <v>15</v>
@@ -9883,7 +9887,7 @@
         <v>202</v>
       </c>
       <c r="C374" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D374" t="s">
         <v>15</v>
@@ -9900,7 +9904,7 @@
         <v>202</v>
       </c>
       <c r="C375" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D375" t="s">
         <v>15</v>
@@ -9917,7 +9921,7 @@
         <v>202</v>
       </c>
       <c r="C376" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D376" t="s">
         <v>15</v>
@@ -10053,7 +10057,7 @@
         <v>202</v>
       </c>
       <c r="C384" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D384" t="s">
         <v>15</v>
@@ -10070,7 +10074,7 @@
         <v>202</v>
       </c>
       <c r="C385" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D385" t="s">
         <v>15</v>
@@ -10087,7 +10091,7 @@
         <v>202</v>
       </c>
       <c r="C386" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D386" t="s">
         <v>15</v>
@@ -10223,7 +10227,7 @@
         <v>202</v>
       </c>
       <c r="C394" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D394" t="s">
         <v>15</v>
@@ -10240,7 +10244,7 @@
         <v>202</v>
       </c>
       <c r="C395" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D395" t="s">
         <v>15</v>
@@ -10257,7 +10261,7 @@
         <v>202</v>
       </c>
       <c r="C396" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D396" t="s">
         <v>15</v>
@@ -10445,7 +10449,7 @@
         <v>504</v>
       </c>
       <c r="C406" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E406" t="s">
         <v>130</v>
@@ -10512,13 +10516,13 @@
         <v>504</v>
       </c>
       <c r="C408" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D408">
         <v>1</v>
       </c>
       <c r="E408" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F408" t="s">
         <v>17</v>
@@ -10547,13 +10551,13 @@
         <v>504</v>
       </c>
       <c r="C409" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D409">
         <v>1</v>
       </c>
       <c r="E409" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F409" t="s">
         <v>17</v>
@@ -10582,7 +10586,7 @@
         <v>504</v>
       </c>
       <c r="C410" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D410">
         <v>1</v>
@@ -10591,7 +10595,7 @@
         <v>510</v>
       </c>
       <c r="F410" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G410" t="s">
         <v>511</v>
@@ -10620,7 +10624,7 @@
         <v>504</v>
       </c>
       <c r="C411" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D411">
         <v>1</v>
@@ -10629,7 +10633,7 @@
         <v>514</v>
       </c>
       <c r="F411" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G411" t="s">
         <v>515</v>
@@ -10655,7 +10659,7 @@
         <v>504</v>
       </c>
       <c r="C412" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D412">
         <v>1</v>
@@ -10664,7 +10668,7 @@
         <v>517</v>
       </c>
       <c r="F412" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G412" t="s">
         <v>518</v>
@@ -10690,7 +10694,7 @@
         <v>504</v>
       </c>
       <c r="C413" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D413">
         <v>1</v>
@@ -10699,7 +10703,7 @@
         <v>519</v>
       </c>
       <c r="F413" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G413" t="s">
         <v>518</v>
@@ -10725,7 +10729,7 @@
         <v>504</v>
       </c>
       <c r="C414" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D414">
         <v>1</v>
@@ -10734,7 +10738,7 @@
         <v>520</v>
       </c>
       <c r="F414" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G414" t="s">
         <v>518</v>
@@ -10769,7 +10773,7 @@
         <v>521</v>
       </c>
       <c r="F415" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G415" t="s">
         <v>518</v>
@@ -10804,7 +10808,7 @@
         <v>522</v>
       </c>
       <c r="F416" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G416" t="s">
         <v>515</v>
@@ -10830,7 +10834,7 @@
         <v>504</v>
       </c>
       <c r="C417" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D417">
         <v>1</v>
@@ -10839,7 +10843,7 @@
         <v>523</v>
       </c>
       <c r="F417" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G417" t="s">
         <v>515</v>
@@ -10874,7 +10878,7 @@
         <v>524</v>
       </c>
       <c r="F418" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G418" t="s">
         <v>525</v>
@@ -10909,7 +10913,7 @@
         <v>526</v>
       </c>
       <c r="F419" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G419" t="s">
         <v>525</v>
@@ -10935,7 +10939,7 @@
         <v>504</v>
       </c>
       <c r="C420" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D420">
         <v>1</v>
@@ -10944,7 +10948,7 @@
         <v>527</v>
       </c>
       <c r="F420" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G420" t="s">
         <v>518</v>
@@ -10999,10 +11003,10 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B422" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C422" t="s">
         <v>14</v>
@@ -11017,7 +11021,7 @@
         <v>17</v>
       </c>
       <c r="G422" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H422" t="s">
         <v>19</v>
@@ -11034,13 +11038,13 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B423" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C423" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E423" t="s">
         <v>130</v>
@@ -11066,10 +11070,10 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B424" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C424" t="s">
         <v>14</v>
@@ -11087,7 +11091,7 @@
         <v>19</v>
       </c>
       <c r="H424" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I424">
         <v>6047</v>
@@ -11101,25 +11105,25 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B425" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C425" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D425">
         <v>1</v>
       </c>
       <c r="E425" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F425" t="s">
         <v>17</v>
       </c>
       <c r="G425" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H425" t="s">
         <v>19</v>
@@ -11136,42 +11140,42 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B426" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C426" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D426">
         <v>1</v>
       </c>
       <c r="E426" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B427" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C427" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D427">
         <v>1</v>
       </c>
       <c r="E427" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F427" t="s">
         <v>17</v>
       </c>
       <c r="G427" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H427" t="s">
         <v>19</v>
@@ -11188,28 +11192,28 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B428" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C428" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D428">
         <v>1</v>
       </c>
       <c r="E428" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F428" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G428" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H428" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I428">
         <v>5919</v>
@@ -11223,25 +11227,25 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B429" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C429" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D429">
         <v>1</v>
       </c>
       <c r="E429" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F429" t="s">
         <v>17</v>
       </c>
       <c r="G429" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H429" t="s">
         <v>19</v>
@@ -11258,28 +11262,28 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B430" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C430" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D430">
         <v>1</v>
       </c>
       <c r="E430" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F430" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G430" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H430" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I430">
         <v>6032</v>
@@ -11293,28 +11297,28 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B431" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C431" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D431">
         <v>1</v>
       </c>
       <c r="E431" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F431" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G431" t="s">
         <v>19</v>
       </c>
       <c r="H431" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I431">
         <v>5900</v>
@@ -11328,10 +11332,10 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B432" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C432" t="s">
         <v>162</v>
@@ -11340,16 +11344,16 @@
         <v>1</v>
       </c>
       <c r="E432" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F432" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G432" t="s">
         <v>19</v>
       </c>
       <c r="H432" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="I432">
         <v>1512</v>
@@ -11366,25 +11370,25 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B433" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C433" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D433">
         <v>1</v>
       </c>
       <c r="E433" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F433" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G433" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H433" t="s">
         <v>512</v>
@@ -11401,25 +11405,25 @@
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B434" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C434" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D434">
         <v>1</v>
       </c>
       <c r="E434" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F434" t="s">
         <v>17</v>
       </c>
       <c r="G434" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H434" t="s">
         <v>19</v>
@@ -11436,10 +11440,10 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B435" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C435" t="s">
         <v>14</v>
@@ -11457,7 +11461,7 @@
         <v>19</v>
       </c>
       <c r="H435" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I435">
         <v>6047</v>
@@ -11471,25 +11475,25 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
+        <v>548</v>
+      </c>
+      <c r="B436" t="s">
+        <v>530</v>
+      </c>
+      <c r="C436" t="s">
+        <v>95</v>
+      </c>
+      <c r="D436" t="s">
+        <v>549</v>
+      </c>
+      <c r="E436" t="s">
         <v>550</v>
-      </c>
-      <c r="B436" t="s">
-        <v>532</v>
-      </c>
-      <c r="C436" t="s">
-        <v>94</v>
-      </c>
-      <c r="D436" t="s">
-        <v>529</v>
-      </c>
-      <c r="E436" t="s">
-        <v>530</v>
       </c>
       <c r="F436" t="s">
         <v>17</v>
       </c>
       <c r="G436" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H436" t="s">
         <v>19</v>
@@ -11506,22 +11510,22 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B437" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C437" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D437" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E437" t="s">
         <v>551</v>
       </c>
       <c r="F437" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G437" t="s">
         <v>19</v>
@@ -11541,10 +11545,10 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B438" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C438" t="s">
         <v>162</v>
@@ -11556,7 +11560,7 @@
         <v>553</v>
       </c>
       <c r="F438" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G438" t="s">
         <v>19</v>
@@ -11579,13 +11583,13 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B439" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C439" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D439">
         <v>2</v>
@@ -11594,7 +11598,7 @@
         <v>556</v>
       </c>
       <c r="F439" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G439" t="s">
         <v>19</v>
@@ -11617,13 +11621,13 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B440" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C440" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D440">
         <v>4</v>
@@ -11655,13 +11659,13 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B441" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C441" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D441">
         <v>4</v>
@@ -11691,15 +11695,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B442" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C442" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D442">
         <v>4</v>
@@ -11708,7 +11712,7 @@
         <v>563</v>
       </c>
       <c r="F442" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G442" t="s">
         <v>564</v>
@@ -11734,7 +11738,7 @@
         <v>566</v>
       </c>
       <c r="B443" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C443" t="s">
         <v>14</v>
@@ -11749,7 +11753,7 @@
         <v>17</v>
       </c>
       <c r="G443" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H443" t="s">
         <v>19</v>
@@ -11769,10 +11773,10 @@
         <v>566</v>
       </c>
       <c r="B444" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C444" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E444" t="s">
         <v>130</v>
@@ -11801,7 +11805,7 @@
         <v>566</v>
       </c>
       <c r="B445" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C445" t="s">
         <v>14</v>
@@ -11819,7 +11823,7 @@
         <v>19</v>
       </c>
       <c r="H445" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I445">
         <v>14337</v>
@@ -11836,16 +11840,16 @@
         <v>566</v>
       </c>
       <c r="B446" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C446" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D446">
         <v>1</v>
       </c>
       <c r="E446" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F446" t="s">
         <v>17</v>
@@ -11871,16 +11875,16 @@
         <v>566</v>
       </c>
       <c r="B447" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C447" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D447">
         <v>1</v>
       </c>
       <c r="E447" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.3">
@@ -11888,16 +11892,16 @@
         <v>566</v>
       </c>
       <c r="B448" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C448" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D448">
         <v>1</v>
       </c>
       <c r="E448" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F448" t="s">
         <v>17</v>
@@ -11923,10 +11927,10 @@
         <v>566</v>
       </c>
       <c r="B449" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C449" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D449">
         <v>1</v>
@@ -11935,7 +11939,7 @@
         <v>569</v>
       </c>
       <c r="F449" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G449" t="s">
         <v>19</v>
@@ -11958,7 +11962,7 @@
         <v>566</v>
       </c>
       <c r="B450" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C450" t="s">
         <v>14</v>
@@ -11993,16 +11997,16 @@
         <v>566</v>
       </c>
       <c r="B451" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C451" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D451" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E451" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="F451" t="s">
         <v>17</v>
@@ -12066,7 +12070,7 @@
         <v>573</v>
       </c>
       <c r="C453" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E453" t="s">
         <v>130</v>
@@ -12133,13 +12137,13 @@
         <v>573</v>
       </c>
       <c r="C455" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D455">
         <v>1</v>
       </c>
       <c r="E455" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F455" t="s">
         <v>17</v>
@@ -12168,13 +12172,13 @@
         <v>573</v>
       </c>
       <c r="C456" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D456">
         <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F456" t="s">
         <v>17</v>
@@ -12203,7 +12207,7 @@
         <v>573</v>
       </c>
       <c r="C457" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D457">
         <v>1</v>
@@ -12220,7 +12224,7 @@
         <v>573</v>
       </c>
       <c r="C458" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D458">
         <v>1</v>
@@ -12237,7 +12241,7 @@
         <v>573</v>
       </c>
       <c r="C459" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D459">
         <v>1</v>
@@ -12254,7 +12258,7 @@
         <v>573</v>
       </c>
       <c r="C460" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D460">
         <v>1</v>
@@ -12280,7 +12284,7 @@
         <v>581</v>
       </c>
       <c r="F461" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G461" t="s">
         <v>582</v>
@@ -12295,7 +12299,7 @@
         <v>11374</v>
       </c>
       <c r="K461" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L461" t="b">
         <v>1</v>
@@ -12318,7 +12322,7 @@
         <v>583</v>
       </c>
       <c r="F462" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G462" t="s">
         <v>584</v>
@@ -12333,7 +12337,7 @@
         <v>11374</v>
       </c>
       <c r="K462" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L462" t="b">
         <v>1</v>
@@ -12356,7 +12360,7 @@
         <v>585</v>
       </c>
       <c r="F463" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G463" t="s">
         <v>584</v>
@@ -12371,7 +12375,7 @@
         <v>11374</v>
       </c>
       <c r="K463" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L463" t="b">
         <v>1</v>
@@ -12429,7 +12433,7 @@
         <v>588</v>
       </c>
       <c r="F465" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G465" t="s">
         <v>589</v>
@@ -12464,7 +12468,7 @@
         <v>590</v>
       </c>
       <c r="F466" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G466" t="s">
         <v>589</v>
@@ -12499,13 +12503,13 @@
         <v>591</v>
       </c>
       <c r="F467" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G467" t="s">
         <v>592</v>
       </c>
       <c r="H467" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I467">
         <v>8510</v>
@@ -12534,13 +12538,13 @@
         <v>593</v>
       </c>
       <c r="F468" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G468" t="s">
         <v>592</v>
       </c>
       <c r="H468" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I468">
         <v>8516</v>
@@ -12569,7 +12573,7 @@
         <v>594</v>
       </c>
       <c r="F469" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G469" t="s">
         <v>589</v>
@@ -12604,7 +12608,7 @@
         <v>595</v>
       </c>
       <c r="F470" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G470" t="s">
         <v>589</v>
@@ -12630,7 +12634,7 @@
         <v>573</v>
       </c>
       <c r="C471" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D471">
         <v>1</v>
@@ -12639,13 +12643,13 @@
         <v>596</v>
       </c>
       <c r="F471" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G471" t="s">
         <v>597</v>
       </c>
       <c r="H471" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I471">
         <v>8552</v>
@@ -12700,7 +12704,7 @@
         <v>573</v>
       </c>
       <c r="C473" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D473">
         <v>1</v>
@@ -12709,7 +12713,7 @@
         <v>600</v>
       </c>
       <c r="F473" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G473" t="s">
         <v>584</v>
@@ -12724,7 +12728,7 @@
         <v>11374</v>
       </c>
       <c r="K473" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L473" t="b">
         <v>1</v>
@@ -12764,13 +12768,13 @@
         <v>602</v>
       </c>
       <c r="F475" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G475" t="s">
         <v>597</v>
       </c>
       <c r="H475" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I475">
         <v>5546</v>
@@ -12814,7 +12818,7 @@
         <v>11374</v>
       </c>
       <c r="K476" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L476" t="b">
         <v>1</v>
@@ -12906,7 +12910,7 @@
         <v>609</v>
       </c>
       <c r="F480" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G480" t="s">
         <v>589</v>
@@ -12941,7 +12945,7 @@
         <v>610</v>
       </c>
       <c r="F481" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G481" t="s">
         <v>611</v>
@@ -12956,7 +12960,7 @@
         <v>11374</v>
       </c>
       <c r="K481" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L481" t="b">
         <v>1</v>
@@ -12979,7 +12983,7 @@
         <v>613</v>
       </c>
       <c r="F482" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G482" t="s">
         <v>614</v>
@@ -12994,7 +12998,7 @@
         <v>11374</v>
       </c>
       <c r="K482" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L482" t="b">
         <v>1</v>
@@ -13017,7 +13021,7 @@
         <v>615</v>
       </c>
       <c r="F483" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G483" t="s">
         <v>616</v>
@@ -13032,7 +13036,7 @@
         <v>11374</v>
       </c>
       <c r="K483" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L483" t="b">
         <v>1</v>
@@ -13055,7 +13059,7 @@
         <v>618</v>
       </c>
       <c r="F484" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G484" t="s">
         <v>584</v>
@@ -13070,7 +13074,7 @@
         <v>11374</v>
       </c>
       <c r="K484" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L484" t="b">
         <v>1</v>
@@ -13093,7 +13097,7 @@
         <v>619</v>
       </c>
       <c r="F485" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G485" t="s">
         <v>620</v>
@@ -13119,7 +13123,7 @@
         <v>573</v>
       </c>
       <c r="C486" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D486">
         <v>1</v>
@@ -13128,7 +13132,7 @@
         <v>622</v>
       </c>
       <c r="F486" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G486" t="s">
         <v>623</v>
@@ -13143,7 +13147,7 @@
         <v>11374</v>
       </c>
       <c r="K486" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L486" t="b">
         <v>1</v>
@@ -13192,13 +13196,13 @@
         <v>573</v>
       </c>
       <c r="C488" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D488" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E488" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="F488" t="s">
         <v>17</v>
@@ -13230,13 +13234,13 @@
         <v>162</v>
       </c>
       <c r="D489" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E489" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F489" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G489" t="s">
         <v>511</v>
@@ -13265,16 +13269,16 @@
         <v>162</v>
       </c>
       <c r="D490" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E490" t="s">
+        <v>627</v>
+      </c>
+      <c r="F490" t="s">
+        <v>34</v>
+      </c>
+      <c r="G490" t="s">
         <v>628</v>
-      </c>
-      <c r="F490" t="s">
-        <v>33</v>
-      </c>
-      <c r="G490" t="s">
-        <v>629</v>
       </c>
       <c r="H490" t="s">
         <v>136</v>
@@ -13303,19 +13307,19 @@
         <v>162</v>
       </c>
       <c r="D491" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="E491" t="s">
+        <v>629</v>
+      </c>
+      <c r="F491" t="s">
+        <v>34</v>
+      </c>
+      <c r="G491" t="s">
         <v>630</v>
       </c>
-      <c r="F491" t="s">
-        <v>33</v>
-      </c>
-      <c r="G491" t="s">
+      <c r="H491" t="s">
         <v>631</v>
-      </c>
-      <c r="H491" t="s">
-        <v>632</v>
       </c>
       <c r="I491">
         <v>10759</v>
@@ -13338,13 +13342,13 @@
         <v>573</v>
       </c>
       <c r="C492" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D492">
         <v>2</v>
       </c>
       <c r="E492" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.3">
@@ -13355,7 +13359,7 @@
         <v>573</v>
       </c>
       <c r="C493" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D493">
         <v>3</v>
@@ -13364,7 +13368,7 @@
         <v>633</v>
       </c>
       <c r="F493" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G493" t="s">
         <v>634</v>
@@ -13416,5 +13420,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/raimondo_reggio_ifabfoundation_org/Documents/Desktop/GitHub/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_7D917707D474AA0E62355476585DCE3A8743D975" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2389093E-9595-4B32-8DF4-74FDB9F937A7}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_7D917707D474AA0E62355476585DCE3A8743D975" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBFE0B24-1AB8-414A-8525-BAD601FC9C77}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4080" yWindow="-17715" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="642">
   <si>
     <t>file_name</t>
   </si>
@@ -1944,13 +1944,28 @@
   </si>
   <si>
     <t>941.0, 1.0</t>
+  </si>
+  <si>
+    <t>1,GO,1</t>
+  </si>
+  <si>
+    <t>VISCODE 2</t>
+  </si>
+  <si>
+    <t>m12', 'm60', 'm24', 'bl', 'm84', 'm48', 'm72', 'm36'</t>
+  </si>
+  <si>
+    <t>ADNI3, ADNI5</t>
+  </si>
+  <si>
+    <t>bl', 'm06', 'm12', 'uns1', 'm18', 'm24', 'm36', 'm48', 'm60','m72', 'sc', 'm84',</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1962,6 +1977,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1999,11 +2028,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2306,7 +2341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L494"/>
+  <dimension ref="A1:L496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.109375" bestFit="1" customWidth="1"/>
@@ -4099,7 +4134,7 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="3" t="s">
         <v>129</v>
       </c>
       <c r="L47" t="b">
@@ -4117,16 +4152,16 @@
         <v>95</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>637</v>
       </c>
       <c r="E48" t="s">
-        <v>28</v>
+        <v>638</v>
       </c>
       <c r="F48" t="s">
         <v>17</v>
       </c>
-      <c r="G48" t="s">
-        <v>132</v>
+      <c r="G48" s="2" t="s">
+        <v>639</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
@@ -4138,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>129</v>
+        <v>640</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -4152,22 +4187,22 @@
         <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="D49" t="s">
         <v>127</v>
       </c>
       <c r="E49" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="F49" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
+        <v>132</v>
+      </c>
+      <c r="H49" t="s">
         <v>19</v>
-      </c>
-      <c r="H49" t="s">
-        <v>41</v>
       </c>
       <c r="I49">
         <v>1247</v>
@@ -4190,28 +4225,28 @@
         <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
         <v>127</v>
       </c>
       <c r="E50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G50" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="I50">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="J50">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K50" t="s">
         <v>129</v>
@@ -4234,22 +4269,22 @@
         <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I51">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K51" t="s">
         <v>129</v>
@@ -4266,22 +4301,22 @@
         <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D52" t="s">
         <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F52" t="s">
         <v>22</v>
       </c>
       <c r="G52" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I52">
         <v>1247</v>
@@ -4304,28 +4339,28 @@
         <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
         <v>127</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="H53" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I53">
-        <v>1214</v>
+        <v>1247</v>
       </c>
       <c r="J53">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K53" t="s">
         <v>129</v>
@@ -4342,13 +4377,13 @@
         <v>126</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
         <v>127</v>
       </c>
       <c r="E54" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
@@ -4357,13 +4392,13 @@
         <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I54">
-        <v>1245</v>
+        <v>1214</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K54" t="s">
         <v>129</v>
@@ -4380,13 +4415,34 @@
         <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="D55" t="s">
         <v>127</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>145</v>
+      </c>
+      <c r="F55" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55">
+        <v>1245</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55" t="s">
+        <v>129</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -4397,13 +4453,13 @@
         <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D56" t="s">
         <v>127</v>
       </c>
       <c r="E56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -4414,13 +4470,13 @@
         <v>126</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D57" t="s">
         <v>127</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -4431,13 +4487,13 @@
         <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
         <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -4448,34 +4504,13 @@
         <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="D59" t="s">
         <v>127</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
-      </c>
-      <c r="F59" t="s">
-        <v>34</v>
-      </c>
-      <c r="G59" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" t="s">
-        <v>148</v>
-      </c>
-      <c r="I59">
-        <v>1240</v>
-      </c>
-      <c r="J59">
-        <v>7</v>
-      </c>
-      <c r="K59" t="s">
-        <v>129</v>
-      </c>
-      <c r="L59" t="b">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -4486,13 +4521,34 @@
         <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="D60" t="s">
         <v>127</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="F60" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>148</v>
+      </c>
+      <c r="I60">
+        <v>1240</v>
+      </c>
+      <c r="J60">
+        <v>7</v>
+      </c>
+      <c r="K60" t="s">
+        <v>129</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -4509,28 +4565,7 @@
         <v>127</v>
       </c>
       <c r="E61" t="s">
-        <v>150</v>
-      </c>
-      <c r="F61" t="s">
-        <v>34</v>
-      </c>
-      <c r="G61" t="s">
-        <v>151</v>
-      </c>
-      <c r="H61" t="s">
-        <v>152</v>
-      </c>
-      <c r="I61">
-        <v>1245</v>
-      </c>
-      <c r="J61">
-        <v>2</v>
-      </c>
-      <c r="K61" t="s">
-        <v>129</v>
-      </c>
-      <c r="L61" t="b">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -4541,28 +4576,28 @@
         <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
         <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F62" t="s">
         <v>34</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="H62" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I62">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="s">
         <v>129</v>
@@ -4579,30 +4614,51 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D63" t="s">
         <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>155</v>
+        <v>153</v>
+      </c>
+      <c r="F63" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>154</v>
+      </c>
+      <c r="I63">
+        <v>1244</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63" t="s">
+        <v>129</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
         <v>127</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -4613,13 +4669,13 @@
         <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
         <v>127</v>
       </c>
       <c r="E65" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -4630,13 +4686,13 @@
         <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D66" t="s">
         <v>127</v>
       </c>
       <c r="E66" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -4647,13 +4703,13 @@
         <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s">
         <v>127</v>
       </c>
       <c r="E67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -4670,7 +4726,7 @@
         <v>127</v>
       </c>
       <c r="E68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -4687,7 +4743,7 @@
         <v>127</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -4698,13 +4754,13 @@
         <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
         <v>127</v>
       </c>
       <c r="E70" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -4715,13 +4771,13 @@
         <v>157</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D71" t="s">
         <v>127</v>
       </c>
       <c r="E71" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -4732,13 +4788,13 @@
         <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="D72" t="s">
         <v>127</v>
       </c>
       <c r="E72" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -4755,7 +4811,7 @@
         <v>127</v>
       </c>
       <c r="E73" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -4766,13 +4822,13 @@
         <v>157</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="D74" t="s">
         <v>127</v>
       </c>
       <c r="E74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -4783,13 +4839,13 @@
         <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D75" t="s">
         <v>127</v>
       </c>
       <c r="E75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -4806,7 +4862,7 @@
         <v>127</v>
       </c>
       <c r="E76" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -4823,7 +4879,7 @@
         <v>127</v>
       </c>
       <c r="E77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -4834,13 +4890,13 @@
         <v>157</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="D78" t="s">
         <v>127</v>
       </c>
       <c r="E78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -4857,7 +4913,7 @@
         <v>127</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -4868,13 +4924,13 @@
         <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="D80" t="s">
         <v>127</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -4885,13 +4941,13 @@
         <v>157</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D81" t="s">
         <v>127</v>
       </c>
       <c r="E81" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -4902,13 +4958,13 @@
         <v>157</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D82" t="s">
         <v>127</v>
       </c>
       <c r="E82" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -4919,13 +4975,13 @@
         <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D83" t="s">
         <v>127</v>
       </c>
       <c r="E83" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -4936,13 +4992,13 @@
         <v>157</v>
       </c>
       <c r="C84" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D84" t="s">
         <v>127</v>
       </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -4953,13 +5009,13 @@
         <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s">
         <v>127</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -4970,13 +5026,13 @@
         <v>157</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D86" t="s">
         <v>127</v>
       </c>
       <c r="E86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -4987,13 +5043,13 @@
         <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D87" t="s">
         <v>127</v>
       </c>
       <c r="E87" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -5010,7 +5066,7 @@
         <v>127</v>
       </c>
       <c r="E88" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -5021,13 +5077,13 @@
         <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D89" t="s">
         <v>127</v>
       </c>
       <c r="E89" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -5044,7 +5100,7 @@
         <v>127</v>
       </c>
       <c r="E90" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -5055,13 +5111,13 @@
         <v>157</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D91" t="s">
         <v>127</v>
       </c>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -5078,7 +5134,7 @@
         <v>127</v>
       </c>
       <c r="E92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -5095,7 +5151,7 @@
         <v>127</v>
       </c>
       <c r="E93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -5112,7 +5168,7 @@
         <v>127</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -5123,13 +5179,13 @@
         <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D95" t="s">
         <v>127</v>
       </c>
       <c r="E95" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -5146,7 +5202,7 @@
         <v>127</v>
       </c>
       <c r="E96" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -5157,13 +5213,13 @@
         <v>157</v>
       </c>
       <c r="C97" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D97" t="s">
         <v>127</v>
       </c>
       <c r="E97" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -5180,7 +5236,7 @@
         <v>127</v>
       </c>
       <c r="E98" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -5191,13 +5247,13 @@
         <v>157</v>
       </c>
       <c r="C99" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="D99" t="s">
         <v>127</v>
       </c>
       <c r="E99" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -5208,13 +5264,13 @@
         <v>157</v>
       </c>
       <c r="C100" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D100" t="s">
         <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -5231,7 +5287,7 @@
         <v>127</v>
       </c>
       <c r="E101" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -5248,7 +5304,7 @@
         <v>127</v>
       </c>
       <c r="E102" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -5265,7 +5321,7 @@
         <v>127</v>
       </c>
       <c r="E103" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -5282,7 +5338,7 @@
         <v>127</v>
       </c>
       <c r="E104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -5293,13 +5349,13 @@
         <v>157</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D105" t="s">
         <v>127</v>
       </c>
       <c r="E105" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -5310,13 +5366,13 @@
         <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D106" t="s">
         <v>127</v>
       </c>
       <c r="E106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -5327,51 +5383,30 @@
         <v>157</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D107" t="s">
         <v>127</v>
       </c>
       <c r="E107" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="E108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F108" t="s">
-        <v>17</v>
-      </c>
-      <c r="G108" t="s">
-        <v>203</v>
-      </c>
-      <c r="H108" t="s">
-        <v>19</v>
-      </c>
-      <c r="I108">
-        <v>121</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
-      </c>
-      <c r="K108" t="s">
-        <v>204</v>
-      </c>
-      <c r="L108" t="b">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -5382,13 +5417,34 @@
         <v>202</v>
       </c>
       <c r="C109" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
       </c>
       <c r="E109" t="s">
-        <v>205</v>
+        <v>16</v>
+      </c>
+      <c r="F109" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" t="s">
+        <v>203</v>
+      </c>
+      <c r="H109" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109">
+        <v>121</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" t="s">
+        <v>204</v>
+      </c>
+      <c r="L109" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -5399,13 +5455,13 @@
         <v>202</v>
       </c>
       <c r="C110" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
       </c>
       <c r="E110" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -5416,13 +5472,13 @@
         <v>202</v>
       </c>
       <c r="C111" t="s">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
       </c>
       <c r="E111" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -5433,13 +5489,13 @@
         <v>202</v>
       </c>
       <c r="C112" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
       </c>
       <c r="E112" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -5450,13 +5506,13 @@
         <v>202</v>
       </c>
       <c r="C113" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
       </c>
       <c r="E113" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -5473,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="E114" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -5490,7 +5546,7 @@
         <v>15</v>
       </c>
       <c r="E115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -5507,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -5524,7 +5580,7 @@
         <v>15</v>
       </c>
       <c r="E117" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -5541,7 +5597,7 @@
         <v>15</v>
       </c>
       <c r="E118" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -5558,7 +5614,7 @@
         <v>15</v>
       </c>
       <c r="E119" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -5575,7 +5631,7 @@
         <v>15</v>
       </c>
       <c r="E120" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -5592,7 +5648,7 @@
         <v>15</v>
       </c>
       <c r="E121" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -5609,7 +5665,7 @@
         <v>15</v>
       </c>
       <c r="E122" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -5626,7 +5682,7 @@
         <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -5643,7 +5699,7 @@
         <v>15</v>
       </c>
       <c r="E124" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -5660,7 +5716,7 @@
         <v>15</v>
       </c>
       <c r="E125" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -5677,7 +5733,7 @@
         <v>15</v>
       </c>
       <c r="E126" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -5694,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="E127" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -5711,7 +5767,7 @@
         <v>15</v>
       </c>
       <c r="E128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -5728,7 +5784,7 @@
         <v>15</v>
       </c>
       <c r="E129" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -5745,7 +5801,7 @@
         <v>15</v>
       </c>
       <c r="E130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -5762,7 +5818,7 @@
         <v>15</v>
       </c>
       <c r="E131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -5779,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="E132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -5796,7 +5852,7 @@
         <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -5813,7 +5869,7 @@
         <v>15</v>
       </c>
       <c r="E134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -5830,7 +5886,7 @@
         <v>15</v>
       </c>
       <c r="E135" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -5841,13 +5897,13 @@
         <v>202</v>
       </c>
       <c r="C136" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="D136" t="s">
         <v>15</v>
       </c>
       <c r="E136" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -5858,13 +5914,13 @@
         <v>202</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="D137" t="s">
         <v>15</v>
       </c>
       <c r="E137" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -5875,13 +5931,13 @@
         <v>202</v>
       </c>
       <c r="C138" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="D138" t="s">
         <v>15</v>
       </c>
       <c r="E138" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -5892,13 +5948,13 @@
         <v>202</v>
       </c>
       <c r="C139" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="D139" t="s">
         <v>15</v>
       </c>
       <c r="E139" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -5915,7 +5971,7 @@
         <v>15</v>
       </c>
       <c r="E140" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -5932,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="E141" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -5949,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="E142" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -5966,7 +6022,7 @@
         <v>15</v>
       </c>
       <c r="E143" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -5983,7 +6039,7 @@
         <v>15</v>
       </c>
       <c r="E144" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -6000,7 +6056,7 @@
         <v>15</v>
       </c>
       <c r="E145" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
@@ -6017,7 +6073,7 @@
         <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
@@ -6034,7 +6090,7 @@
         <v>15</v>
       </c>
       <c r="E147" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
@@ -6051,7 +6107,7 @@
         <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
@@ -6068,7 +6124,7 @@
         <v>15</v>
       </c>
       <c r="E149" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
@@ -6085,7 +6141,7 @@
         <v>15</v>
       </c>
       <c r="E150" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
@@ -6102,7 +6158,7 @@
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
@@ -6119,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="E152" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -6136,7 +6192,7 @@
         <v>15</v>
       </c>
       <c r="E153" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
@@ -6147,13 +6203,13 @@
         <v>202</v>
       </c>
       <c r="C154" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="D154" t="s">
         <v>15</v>
       </c>
       <c r="E154" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -6164,13 +6220,13 @@
         <v>202</v>
       </c>
       <c r="C155" t="s">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="D155" t="s">
         <v>15</v>
       </c>
       <c r="E155" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -6181,13 +6237,13 @@
         <v>202</v>
       </c>
       <c r="C156" t="s">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -6204,7 +6260,7 @@
         <v>15</v>
       </c>
       <c r="E157" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
@@ -6221,7 +6277,7 @@
         <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
@@ -6238,7 +6294,7 @@
         <v>15</v>
       </c>
       <c r="E159" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -6249,13 +6305,13 @@
         <v>202</v>
       </c>
       <c r="C160" t="s">
-        <v>257</v>
+        <v>162</v>
       </c>
       <c r="D160" t="s">
         <v>15</v>
       </c>
       <c r="E160" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -6266,13 +6322,13 @@
         <v>202</v>
       </c>
       <c r="C161" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="D161" t="s">
         <v>15</v>
       </c>
       <c r="E161" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -6289,7 +6345,7 @@
         <v>15</v>
       </c>
       <c r="E162" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
@@ -6300,13 +6356,13 @@
         <v>202</v>
       </c>
       <c r="C163" t="s">
-        <v>257</v>
+        <v>162</v>
       </c>
       <c r="D163" t="s">
         <v>15</v>
       </c>
       <c r="E163" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
@@ -6317,13 +6373,13 @@
         <v>202</v>
       </c>
       <c r="C164" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="D164" t="s">
         <v>15</v>
       </c>
       <c r="E164" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
@@ -6334,13 +6390,13 @@
         <v>202</v>
       </c>
       <c r="C165" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="D165" t="s">
         <v>15</v>
       </c>
       <c r="E165" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
@@ -6357,7 +6413,7 @@
         <v>15</v>
       </c>
       <c r="E166" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
@@ -6368,13 +6424,13 @@
         <v>202</v>
       </c>
       <c r="C167" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="D167" t="s">
         <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -6385,13 +6441,13 @@
         <v>202</v>
       </c>
       <c r="C168" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
       </c>
       <c r="E168" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -6402,13 +6458,13 @@
         <v>202</v>
       </c>
       <c r="C169" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
@@ -6425,7 +6481,7 @@
         <v>15</v>
       </c>
       <c r="E170" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
@@ -6442,7 +6498,7 @@
         <v>15</v>
       </c>
       <c r="E171" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
@@ -6453,13 +6509,13 @@
         <v>202</v>
       </c>
       <c r="C172" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D172" t="s">
         <v>15</v>
       </c>
       <c r="E172" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
@@ -6470,13 +6526,13 @@
         <v>202</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D173" t="s">
         <v>15</v>
       </c>
       <c r="E173" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
@@ -6493,7 +6549,7 @@
         <v>15</v>
       </c>
       <c r="E174" t="s">
-        <v>198</v>
+        <v>271</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
@@ -6504,13 +6560,13 @@
         <v>202</v>
       </c>
       <c r="C175" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="D175" t="s">
         <v>15</v>
       </c>
       <c r="E175" t="s">
-        <v>272</v>
+        <v>198</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
@@ -6527,7 +6583,7 @@
         <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -6538,13 +6594,13 @@
         <v>202</v>
       </c>
       <c r="C177" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D177" t="s">
         <v>15</v>
       </c>
       <c r="E177" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
@@ -6555,13 +6611,13 @@
         <v>202</v>
       </c>
       <c r="C178" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="D178" t="s">
         <v>15</v>
       </c>
       <c r="E178" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
@@ -6572,13 +6628,13 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D179" t="s">
         <v>15</v>
       </c>
       <c r="E179" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -6595,7 +6651,7 @@
         <v>15</v>
       </c>
       <c r="E180" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
@@ -6612,7 +6668,7 @@
         <v>15</v>
       </c>
       <c r="E181" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -6629,7 +6685,7 @@
         <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
@@ -6646,7 +6702,7 @@
         <v>15</v>
       </c>
       <c r="E183" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
@@ -6657,13 +6713,13 @@
         <v>202</v>
       </c>
       <c r="C184" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="D184" t="s">
         <v>15</v>
       </c>
       <c r="E184" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
@@ -6680,7 +6736,7 @@
         <v>15</v>
       </c>
       <c r="E185" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
@@ -6697,7 +6753,7 @@
         <v>15</v>
       </c>
       <c r="E186" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
@@ -6708,13 +6764,13 @@
         <v>202</v>
       </c>
       <c r="C187" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D187" t="s">
         <v>15</v>
       </c>
       <c r="E187" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -6731,7 +6787,7 @@
         <v>15</v>
       </c>
       <c r="E188" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -6742,13 +6798,13 @@
         <v>202</v>
       </c>
       <c r="C189" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D189" t="s">
         <v>15</v>
       </c>
       <c r="E189" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
@@ -6765,7 +6821,7 @@
         <v>15</v>
       </c>
       <c r="E190" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
@@ -6776,13 +6832,13 @@
         <v>202</v>
       </c>
       <c r="C191" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D191" t="s">
         <v>15</v>
       </c>
       <c r="E191" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
@@ -6799,7 +6855,7 @@
         <v>15</v>
       </c>
       <c r="E192" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
@@ -6816,7 +6872,7 @@
         <v>15</v>
       </c>
       <c r="E193" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
@@ -6827,13 +6883,13 @@
         <v>202</v>
       </c>
       <c r="C194" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D194" t="s">
         <v>15</v>
       </c>
       <c r="E194" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
@@ -6850,7 +6906,7 @@
         <v>15</v>
       </c>
       <c r="E195" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
@@ -6867,7 +6923,7 @@
         <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
@@ -6878,13 +6934,13 @@
         <v>202</v>
       </c>
       <c r="C197" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D197" t="s">
         <v>15</v>
       </c>
       <c r="E197" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
@@ -6901,7 +6957,7 @@
         <v>15</v>
       </c>
       <c r="E198" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
@@ -6912,13 +6968,13 @@
         <v>202</v>
       </c>
       <c r="C199" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
       </c>
       <c r="E199" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
@@ -6935,7 +6991,7 @@
         <v>15</v>
       </c>
       <c r="E200" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
@@ -6946,13 +7002,13 @@
         <v>202</v>
       </c>
       <c r="C201" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D201" t="s">
         <v>15</v>
       </c>
       <c r="E201" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
@@ -6969,7 +7025,7 @@
         <v>15</v>
       </c>
       <c r="E202" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
@@ -6986,7 +7042,7 @@
         <v>15</v>
       </c>
       <c r="E203" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -6997,13 +7053,13 @@
         <v>202</v>
       </c>
       <c r="C204" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D204" t="s">
         <v>15</v>
       </c>
       <c r="E204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -7020,7 +7076,7 @@
         <v>15</v>
       </c>
       <c r="E205" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -7037,7 +7093,7 @@
         <v>15</v>
       </c>
       <c r="E206" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -7048,13 +7104,13 @@
         <v>202</v>
       </c>
       <c r="C207" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D207" t="s">
         <v>15</v>
       </c>
       <c r="E207" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
@@ -7071,7 +7127,7 @@
         <v>15</v>
       </c>
       <c r="E208" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
@@ -7082,13 +7138,13 @@
         <v>202</v>
       </c>
       <c r="C209" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D209" t="s">
         <v>15</v>
       </c>
       <c r="E209" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
@@ -7105,7 +7161,7 @@
         <v>15</v>
       </c>
       <c r="E210" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
@@ -7116,13 +7172,13 @@
         <v>202</v>
       </c>
       <c r="C211" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D211" t="s">
         <v>15</v>
       </c>
       <c r="E211" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
@@ -7139,7 +7195,7 @@
         <v>15</v>
       </c>
       <c r="E212" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
@@ -7156,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="E213" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
@@ -7167,13 +7223,13 @@
         <v>202</v>
       </c>
       <c r="C214" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D214" t="s">
         <v>15</v>
       </c>
       <c r="E214" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
@@ -7190,7 +7246,7 @@
         <v>15</v>
       </c>
       <c r="E215" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
@@ -7207,7 +7263,7 @@
         <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
@@ -7218,13 +7274,13 @@
         <v>202</v>
       </c>
       <c r="C217" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D217" t="s">
         <v>15</v>
       </c>
       <c r="E217" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
@@ -7241,7 +7297,7 @@
         <v>15</v>
       </c>
       <c r="E218" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
@@ -7252,13 +7308,13 @@
         <v>202</v>
       </c>
       <c r="C219" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D219" t="s">
         <v>15</v>
       </c>
       <c r="E219" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
@@ -7275,7 +7331,7 @@
         <v>15</v>
       </c>
       <c r="E220" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
@@ -7286,13 +7342,13 @@
         <v>202</v>
       </c>
       <c r="C221" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D221" t="s">
         <v>15</v>
       </c>
       <c r="E221" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
@@ -7309,7 +7365,7 @@
         <v>15</v>
       </c>
       <c r="E222" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
@@ -7326,7 +7382,7 @@
         <v>15</v>
       </c>
       <c r="E223" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
@@ -7337,13 +7393,13 @@
         <v>202</v>
       </c>
       <c r="C224" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
       </c>
       <c r="E224" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
@@ -7360,7 +7416,7 @@
         <v>15</v>
       </c>
       <c r="E225" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -7377,7 +7433,7 @@
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
@@ -7388,13 +7444,13 @@
         <v>202</v>
       </c>
       <c r="C227" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D227" t="s">
         <v>15</v>
       </c>
       <c r="E227" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
@@ -7411,7 +7467,7 @@
         <v>15</v>
       </c>
       <c r="E228" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
@@ -7422,13 +7478,13 @@
         <v>202</v>
       </c>
       <c r="C229" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D229" t="s">
         <v>15</v>
       </c>
       <c r="E229" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -7445,7 +7501,7 @@
         <v>15</v>
       </c>
       <c r="E230" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
@@ -7456,13 +7512,13 @@
         <v>202</v>
       </c>
       <c r="C231" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D231" t="s">
         <v>15</v>
       </c>
       <c r="E231" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
@@ -7479,7 +7535,7 @@
         <v>15</v>
       </c>
       <c r="E232" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -7496,7 +7552,7 @@
         <v>15</v>
       </c>
       <c r="E233" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
@@ -7507,13 +7563,13 @@
         <v>202</v>
       </c>
       <c r="C234" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D234" t="s">
         <v>15</v>
       </c>
       <c r="E234" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
@@ -7530,7 +7586,7 @@
         <v>15</v>
       </c>
       <c r="E235" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -7547,7 +7603,7 @@
         <v>15</v>
       </c>
       <c r="E236" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
@@ -7558,13 +7614,13 @@
         <v>202</v>
       </c>
       <c r="C237" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D237" t="s">
         <v>15</v>
       </c>
       <c r="E237" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
@@ -7581,7 +7637,7 @@
         <v>15</v>
       </c>
       <c r="E238" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
@@ -7592,13 +7648,13 @@
         <v>202</v>
       </c>
       <c r="C239" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D239" t="s">
         <v>15</v>
       </c>
       <c r="E239" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
@@ -7615,7 +7671,7 @@
         <v>15</v>
       </c>
       <c r="E240" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
@@ -7626,13 +7682,13 @@
         <v>202</v>
       </c>
       <c r="C241" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D241" t="s">
         <v>15</v>
       </c>
       <c r="E241" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
@@ -7649,7 +7705,7 @@
         <v>15</v>
       </c>
       <c r="E242" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
@@ -7666,7 +7722,7 @@
         <v>15</v>
       </c>
       <c r="E243" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
@@ -7677,13 +7733,13 @@
         <v>202</v>
       </c>
       <c r="C244" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D244" t="s">
         <v>15</v>
       </c>
       <c r="E244" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
@@ -7700,7 +7756,7 @@
         <v>15</v>
       </c>
       <c r="E245" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
@@ -7717,7 +7773,7 @@
         <v>15</v>
       </c>
       <c r="E246" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
@@ -7728,13 +7784,13 @@
         <v>202</v>
       </c>
       <c r="C247" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D247" t="s">
         <v>15</v>
       </c>
       <c r="E247" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
@@ -7751,7 +7807,7 @@
         <v>15</v>
       </c>
       <c r="E248" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
@@ -7762,13 +7818,13 @@
         <v>202</v>
       </c>
       <c r="C249" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D249" t="s">
         <v>15</v>
       </c>
       <c r="E249" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
@@ -7785,7 +7841,7 @@
         <v>15</v>
       </c>
       <c r="E250" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
@@ -7796,13 +7852,13 @@
         <v>202</v>
       </c>
       <c r="C251" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D251" t="s">
         <v>15</v>
       </c>
       <c r="E251" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
@@ -7819,7 +7875,7 @@
         <v>15</v>
       </c>
       <c r="E252" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
@@ -7836,7 +7892,7 @@
         <v>15</v>
       </c>
       <c r="E253" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
@@ -7847,13 +7903,13 @@
         <v>202</v>
       </c>
       <c r="C254" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D254" t="s">
         <v>15</v>
       </c>
       <c r="E254" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
@@ -7870,7 +7926,7 @@
         <v>15</v>
       </c>
       <c r="E255" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
@@ -7887,7 +7943,7 @@
         <v>15</v>
       </c>
       <c r="E256" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
@@ -7898,13 +7954,13 @@
         <v>202</v>
       </c>
       <c r="C257" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D257" t="s">
         <v>15</v>
       </c>
       <c r="E257" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
@@ -7921,7 +7977,7 @@
         <v>15</v>
       </c>
       <c r="E258" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
@@ -7932,13 +7988,13 @@
         <v>202</v>
       </c>
       <c r="C259" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D259" t="s">
         <v>15</v>
       </c>
       <c r="E259" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
@@ -7955,7 +8011,7 @@
         <v>15</v>
       </c>
       <c r="E260" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
@@ -7966,13 +8022,13 @@
         <v>202</v>
       </c>
       <c r="C261" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D261" t="s">
         <v>15</v>
       </c>
       <c r="E261" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
@@ -7989,7 +8045,7 @@
         <v>15</v>
       </c>
       <c r="E262" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
@@ -8006,7 +8062,7 @@
         <v>15</v>
       </c>
       <c r="E263" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
@@ -8017,13 +8073,13 @@
         <v>202</v>
       </c>
       <c r="C264" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D264" t="s">
         <v>15</v>
       </c>
       <c r="E264" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
@@ -8040,7 +8096,7 @@
         <v>15</v>
       </c>
       <c r="E265" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
@@ -8057,7 +8113,7 @@
         <v>15</v>
       </c>
       <c r="E266" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
@@ -8068,13 +8124,13 @@
         <v>202</v>
       </c>
       <c r="C267" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D267" t="s">
         <v>15</v>
       </c>
       <c r="E267" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
@@ -8091,7 +8147,7 @@
         <v>15</v>
       </c>
       <c r="E268" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
@@ -8102,13 +8158,13 @@
         <v>202</v>
       </c>
       <c r="C269" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D269" t="s">
         <v>15</v>
       </c>
       <c r="E269" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
@@ -8125,7 +8181,7 @@
         <v>15</v>
       </c>
       <c r="E270" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
@@ -8136,13 +8192,13 @@
         <v>202</v>
       </c>
       <c r="C271" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D271" t="s">
         <v>15</v>
       </c>
       <c r="E271" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
@@ -8159,7 +8215,7 @@
         <v>15</v>
       </c>
       <c r="E272" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
@@ -8176,7 +8232,7 @@
         <v>15</v>
       </c>
       <c r="E273" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
@@ -8187,13 +8243,13 @@
         <v>202</v>
       </c>
       <c r="C274" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D274" t="s">
         <v>15</v>
       </c>
       <c r="E274" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
@@ -8210,7 +8266,7 @@
         <v>15</v>
       </c>
       <c r="E275" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
@@ -8227,7 +8283,7 @@
         <v>15</v>
       </c>
       <c r="E276" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
@@ -8238,13 +8294,13 @@
         <v>202</v>
       </c>
       <c r="C277" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D277" t="s">
         <v>15</v>
       </c>
       <c r="E277" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
@@ -8261,7 +8317,7 @@
         <v>15</v>
       </c>
       <c r="E278" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
@@ -8272,13 +8328,13 @@
         <v>202</v>
       </c>
       <c r="C279" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D279" t="s">
         <v>15</v>
       </c>
       <c r="E279" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
@@ -8295,7 +8351,7 @@
         <v>15</v>
       </c>
       <c r="E280" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
@@ -8306,13 +8362,13 @@
         <v>202</v>
       </c>
       <c r="C281" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D281" t="s">
         <v>15</v>
       </c>
       <c r="E281" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
@@ -8329,7 +8385,7 @@
         <v>15</v>
       </c>
       <c r="E282" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
@@ -8346,7 +8402,7 @@
         <v>15</v>
       </c>
       <c r="E283" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
@@ -8357,13 +8413,13 @@
         <v>202</v>
       </c>
       <c r="C284" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D284" t="s">
         <v>15</v>
       </c>
       <c r="E284" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
@@ -8380,7 +8436,7 @@
         <v>15</v>
       </c>
       <c r="E285" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
@@ -8397,7 +8453,7 @@
         <v>15</v>
       </c>
       <c r="E286" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
@@ -8408,13 +8464,13 @@
         <v>202</v>
       </c>
       <c r="C287" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D287" t="s">
         <v>15</v>
       </c>
       <c r="E287" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
@@ -8431,7 +8487,7 @@
         <v>15</v>
       </c>
       <c r="E288" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
@@ -8442,13 +8498,13 @@
         <v>202</v>
       </c>
       <c r="C289" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D289" t="s">
         <v>15</v>
       </c>
       <c r="E289" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
@@ -8465,7 +8521,7 @@
         <v>15</v>
       </c>
       <c r="E290" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
@@ -8476,13 +8532,13 @@
         <v>202</v>
       </c>
       <c r="C291" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D291" t="s">
         <v>15</v>
       </c>
       <c r="E291" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
@@ -8499,7 +8555,7 @@
         <v>15</v>
       </c>
       <c r="E292" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
@@ -8516,7 +8572,7 @@
         <v>15</v>
       </c>
       <c r="E293" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
@@ -8527,13 +8583,13 @@
         <v>202</v>
       </c>
       <c r="C294" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D294" t="s">
         <v>15</v>
       </c>
       <c r="E294" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
@@ -8550,7 +8606,7 @@
         <v>15</v>
       </c>
       <c r="E295" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
@@ -8567,7 +8623,7 @@
         <v>15</v>
       </c>
       <c r="E296" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
@@ -8578,13 +8634,13 @@
         <v>202</v>
       </c>
       <c r="C297" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D297" t="s">
         <v>15</v>
       </c>
       <c r="E297" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
@@ -8601,7 +8657,7 @@
         <v>15</v>
       </c>
       <c r="E298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
@@ -8612,13 +8668,13 @@
         <v>202</v>
       </c>
       <c r="C299" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D299" t="s">
         <v>15</v>
       </c>
       <c r="E299" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
@@ -8635,7 +8691,7 @@
         <v>15</v>
       </c>
       <c r="E300" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
@@ -8646,13 +8702,13 @@
         <v>202</v>
       </c>
       <c r="C301" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D301" t="s">
         <v>15</v>
       </c>
       <c r="E301" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
@@ -8669,7 +8725,7 @@
         <v>15</v>
       </c>
       <c r="E302" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
@@ -8686,7 +8742,7 @@
         <v>15</v>
       </c>
       <c r="E303" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
@@ -8697,13 +8753,13 @@
         <v>202</v>
       </c>
       <c r="C304" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D304" t="s">
         <v>15</v>
       </c>
       <c r="E304" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
@@ -8720,7 +8776,7 @@
         <v>15</v>
       </c>
       <c r="E305" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
@@ -8737,7 +8793,7 @@
         <v>15</v>
       </c>
       <c r="E306" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
@@ -8748,13 +8804,13 @@
         <v>202</v>
       </c>
       <c r="C307" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D307" t="s">
         <v>15</v>
       </c>
       <c r="E307" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
@@ -8771,7 +8827,7 @@
         <v>15</v>
       </c>
       <c r="E308" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
@@ -8782,13 +8838,13 @@
         <v>202</v>
       </c>
       <c r="C309" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D309" t="s">
         <v>15</v>
       </c>
       <c r="E309" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
@@ -8805,7 +8861,7 @@
         <v>15</v>
       </c>
       <c r="E310" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
@@ -8816,13 +8872,13 @@
         <v>202</v>
       </c>
       <c r="C311" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D311" t="s">
         <v>15</v>
       </c>
       <c r="E311" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
@@ -8839,7 +8895,7 @@
         <v>15</v>
       </c>
       <c r="E312" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
@@ -8856,7 +8912,7 @@
         <v>15</v>
       </c>
       <c r="E313" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
@@ -8867,13 +8923,13 @@
         <v>202</v>
       </c>
       <c r="C314" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D314" t="s">
         <v>15</v>
       </c>
       <c r="E314" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
@@ -8890,7 +8946,7 @@
         <v>15</v>
       </c>
       <c r="E315" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
@@ -8907,7 +8963,7 @@
         <v>15</v>
       </c>
       <c r="E316" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
@@ -8918,13 +8974,13 @@
         <v>202</v>
       </c>
       <c r="C317" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D317" t="s">
         <v>15</v>
       </c>
       <c r="E317" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
@@ -8941,7 +8997,7 @@
         <v>15</v>
       </c>
       <c r="E318" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
@@ -8952,13 +9008,13 @@
         <v>202</v>
       </c>
       <c r="C319" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D319" t="s">
         <v>15</v>
       </c>
       <c r="E319" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
@@ -8975,7 +9031,7 @@
         <v>15</v>
       </c>
       <c r="E320" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
@@ -8986,13 +9042,13 @@
         <v>202</v>
       </c>
       <c r="C321" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D321" t="s">
         <v>15</v>
       </c>
       <c r="E321" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
@@ -9009,7 +9065,7 @@
         <v>15</v>
       </c>
       <c r="E322" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
@@ -9026,7 +9082,7 @@
         <v>15</v>
       </c>
       <c r="E323" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
@@ -9037,13 +9093,13 @@
         <v>202</v>
       </c>
       <c r="C324" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D324" t="s">
         <v>15</v>
       </c>
       <c r="E324" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
@@ -9060,7 +9116,7 @@
         <v>15</v>
       </c>
       <c r="E325" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
@@ -9077,7 +9133,7 @@
         <v>15</v>
       </c>
       <c r="E326" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
@@ -9088,13 +9144,13 @@
         <v>202</v>
       </c>
       <c r="C327" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D327" t="s">
         <v>15</v>
       </c>
       <c r="E327" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
@@ -9111,7 +9167,7 @@
         <v>15</v>
       </c>
       <c r="E328" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
@@ -9122,13 +9178,13 @@
         <v>202</v>
       </c>
       <c r="C329" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D329" t="s">
         <v>15</v>
       </c>
       <c r="E329" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
@@ -9145,7 +9201,7 @@
         <v>15</v>
       </c>
       <c r="E330" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
@@ -9156,13 +9212,13 @@
         <v>202</v>
       </c>
       <c r="C331" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D331" t="s">
         <v>15</v>
       </c>
       <c r="E331" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
@@ -9179,7 +9235,7 @@
         <v>15</v>
       </c>
       <c r="E332" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
@@ -9196,7 +9252,7 @@
         <v>15</v>
       </c>
       <c r="E333" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
@@ -9207,13 +9263,13 @@
         <v>202</v>
       </c>
       <c r="C334" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D334" t="s">
         <v>15</v>
       </c>
       <c r="E334" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
@@ -9230,7 +9286,7 @@
         <v>15</v>
       </c>
       <c r="E335" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
@@ -9247,7 +9303,7 @@
         <v>15</v>
       </c>
       <c r="E336" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
@@ -9258,13 +9314,13 @@
         <v>202</v>
       </c>
       <c r="C337" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D337" t="s">
         <v>15</v>
       </c>
       <c r="E337" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
@@ -9281,7 +9337,7 @@
         <v>15</v>
       </c>
       <c r="E338" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
@@ -9292,13 +9348,13 @@
         <v>202</v>
       </c>
       <c r="C339" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D339" t="s">
         <v>15</v>
       </c>
       <c r="E339" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
@@ -9315,7 +9371,7 @@
         <v>15</v>
       </c>
       <c r="E340" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
@@ -9326,13 +9382,13 @@
         <v>202</v>
       </c>
       <c r="C341" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D341" t="s">
         <v>15</v>
       </c>
       <c r="E341" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
@@ -9349,7 +9405,7 @@
         <v>15</v>
       </c>
       <c r="E342" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
@@ -9366,7 +9422,7 @@
         <v>15</v>
       </c>
       <c r="E343" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
@@ -9377,13 +9433,13 @@
         <v>202</v>
       </c>
       <c r="C344" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D344" t="s">
         <v>15</v>
       </c>
       <c r="E344" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
@@ -9400,7 +9456,7 @@
         <v>15</v>
       </c>
       <c r="E345" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
@@ -9417,7 +9473,7 @@
         <v>15</v>
       </c>
       <c r="E346" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
@@ -9428,13 +9484,13 @@
         <v>202</v>
       </c>
       <c r="C347" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D347" t="s">
         <v>15</v>
       </c>
       <c r="E347" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
@@ -9451,7 +9507,7 @@
         <v>15</v>
       </c>
       <c r="E348" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
@@ -9462,13 +9518,13 @@
         <v>202</v>
       </c>
       <c r="C349" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D349" t="s">
         <v>15</v>
       </c>
       <c r="E349" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
@@ -9485,7 +9541,7 @@
         <v>15</v>
       </c>
       <c r="E350" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
@@ -9496,13 +9552,13 @@
         <v>202</v>
       </c>
       <c r="C351" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D351" t="s">
         <v>15</v>
       </c>
       <c r="E351" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
@@ -9519,7 +9575,7 @@
         <v>15</v>
       </c>
       <c r="E352" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
@@ -9536,7 +9592,7 @@
         <v>15</v>
       </c>
       <c r="E353" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
@@ -9547,13 +9603,13 @@
         <v>202</v>
       </c>
       <c r="C354" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D354" t="s">
         <v>15</v>
       </c>
       <c r="E354" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
@@ -9570,7 +9626,7 @@
         <v>15</v>
       </c>
       <c r="E355" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
@@ -9587,7 +9643,7 @@
         <v>15</v>
       </c>
       <c r="E356" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
@@ -9598,13 +9654,13 @@
         <v>202</v>
       </c>
       <c r="C357" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D357" t="s">
         <v>15</v>
       </c>
       <c r="E357" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
@@ -9621,7 +9677,7 @@
         <v>15</v>
       </c>
       <c r="E358" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
@@ -9632,13 +9688,13 @@
         <v>202</v>
       </c>
       <c r="C359" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D359" t="s">
         <v>15</v>
       </c>
       <c r="E359" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
@@ -9655,7 +9711,7 @@
         <v>15</v>
       </c>
       <c r="E360" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
@@ -9666,13 +9722,13 @@
         <v>202</v>
       </c>
       <c r="C361" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D361" t="s">
         <v>15</v>
       </c>
       <c r="E361" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
@@ -9689,7 +9745,7 @@
         <v>15</v>
       </c>
       <c r="E362" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
@@ -9706,7 +9762,7 @@
         <v>15</v>
       </c>
       <c r="E363" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
@@ -9717,13 +9773,13 @@
         <v>202</v>
       </c>
       <c r="C364" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D364" t="s">
         <v>15</v>
       </c>
       <c r="E364" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
@@ -9740,7 +9796,7 @@
         <v>15</v>
       </c>
       <c r="E365" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
@@ -9757,7 +9813,7 @@
         <v>15</v>
       </c>
       <c r="E366" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
@@ -9768,13 +9824,13 @@
         <v>202</v>
       </c>
       <c r="C367" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D367" t="s">
         <v>15</v>
       </c>
       <c r="E367" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
@@ -9791,7 +9847,7 @@
         <v>15</v>
       </c>
       <c r="E368" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
@@ -9802,13 +9858,13 @@
         <v>202</v>
       </c>
       <c r="C369" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D369" t="s">
         <v>15</v>
       </c>
       <c r="E369" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
@@ -9825,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="E370" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.3">
@@ -9836,13 +9892,13 @@
         <v>202</v>
       </c>
       <c r="C371" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D371" t="s">
         <v>15</v>
       </c>
       <c r="E371" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
@@ -9859,7 +9915,7 @@
         <v>15</v>
       </c>
       <c r="E372" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
@@ -9876,7 +9932,7 @@
         <v>15</v>
       </c>
       <c r="E373" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
@@ -9887,13 +9943,13 @@
         <v>202</v>
       </c>
       <c r="C374" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D374" t="s">
         <v>15</v>
       </c>
       <c r="E374" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
@@ -9910,7 +9966,7 @@
         <v>15</v>
       </c>
       <c r="E375" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
@@ -9927,7 +9983,7 @@
         <v>15</v>
       </c>
       <c r="E376" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
@@ -9938,13 +9994,13 @@
         <v>202</v>
       </c>
       <c r="C377" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D377" t="s">
         <v>15</v>
       </c>
       <c r="E377" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
@@ -9961,7 +10017,7 @@
         <v>15</v>
       </c>
       <c r="E378" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.3">
@@ -9972,13 +10028,13 @@
         <v>202</v>
       </c>
       <c r="C379" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D379" t="s">
         <v>15</v>
       </c>
       <c r="E379" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
@@ -9995,7 +10051,7 @@
         <v>15</v>
       </c>
       <c r="E380" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
@@ -10006,13 +10062,13 @@
         <v>202</v>
       </c>
       <c r="C381" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D381" t="s">
         <v>15</v>
       </c>
       <c r="E381" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
@@ -10029,7 +10085,7 @@
         <v>15</v>
       </c>
       <c r="E382" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
@@ -10046,7 +10102,7 @@
         <v>15</v>
       </c>
       <c r="E383" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
@@ -10057,13 +10113,13 @@
         <v>202</v>
       </c>
       <c r="C384" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D384" t="s">
         <v>15</v>
       </c>
       <c r="E384" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
@@ -10080,7 +10136,7 @@
         <v>15</v>
       </c>
       <c r="E385" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
@@ -10097,7 +10153,7 @@
         <v>15</v>
       </c>
       <c r="E386" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
@@ -10108,13 +10164,13 @@
         <v>202</v>
       </c>
       <c r="C387" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D387" t="s">
         <v>15</v>
       </c>
       <c r="E387" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
@@ -10131,7 +10187,7 @@
         <v>15</v>
       </c>
       <c r="E388" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
@@ -10142,13 +10198,13 @@
         <v>202</v>
       </c>
       <c r="C389" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D389" t="s">
         <v>15</v>
       </c>
       <c r="E389" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
@@ -10165,7 +10221,7 @@
         <v>15</v>
       </c>
       <c r="E390" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
@@ -10176,13 +10232,13 @@
         <v>202</v>
       </c>
       <c r="C391" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D391" t="s">
         <v>15</v>
       </c>
       <c r="E391" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
@@ -10199,7 +10255,7 @@
         <v>15</v>
       </c>
       <c r="E392" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
@@ -10216,7 +10272,7 @@
         <v>15</v>
       </c>
       <c r="E393" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
@@ -10227,13 +10283,13 @@
         <v>202</v>
       </c>
       <c r="C394" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D394" t="s">
         <v>15</v>
       </c>
       <c r="E394" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.3">
@@ -10250,7 +10306,7 @@
         <v>15</v>
       </c>
       <c r="E395" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
@@ -10267,7 +10323,7 @@
         <v>15</v>
       </c>
       <c r="E396" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
@@ -10278,13 +10334,13 @@
         <v>202</v>
       </c>
       <c r="C397" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="D397" t="s">
         <v>15</v>
       </c>
       <c r="E397" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
@@ -10301,7 +10357,7 @@
         <v>15</v>
       </c>
       <c r="E398" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
@@ -10312,13 +10368,13 @@
         <v>202</v>
       </c>
       <c r="C399" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="D399" t="s">
         <v>15</v>
       </c>
       <c r="E399" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.3">
@@ -10335,7 +10391,7 @@
         <v>15</v>
       </c>
       <c r="E400" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.3">
@@ -10346,13 +10402,13 @@
         <v>202</v>
       </c>
       <c r="C401" t="s">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D401" t="s">
         <v>15</v>
       </c>
       <c r="E401" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.3">
@@ -10369,7 +10425,7 @@
         <v>15</v>
       </c>
       <c r="E402" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.3">
@@ -10386,7 +10442,7 @@
         <v>15</v>
       </c>
       <c r="E403" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.3">
@@ -10397,48 +10453,30 @@
         <v>202</v>
       </c>
       <c r="C404" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D404" t="s">
         <v>15</v>
       </c>
       <c r="E404" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>503</v>
+        <v>201</v>
       </c>
       <c r="B405" t="s">
-        <v>504</v>
+        <v>202</v>
       </c>
       <c r="C405" t="s">
-        <v>14</v>
-      </c>
-      <c r="D405">
-        <v>1</v>
+        <v>162</v>
+      </c>
+      <c r="D405" t="s">
+        <v>15</v>
       </c>
       <c r="E405" t="s">
-        <v>16</v>
-      </c>
-      <c r="F405" t="s">
-        <v>17</v>
-      </c>
-      <c r="G405" t="s">
-        <v>505</v>
-      </c>
-      <c r="H405" t="s">
-        <v>19</v>
-      </c>
-      <c r="I405">
-        <v>15244</v>
-      </c>
-      <c r="J405">
-        <v>0</v>
-      </c>
-      <c r="L405" t="b">
-        <v>0</v>
+        <v>502</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.3">
@@ -10449,16 +10487,19 @@
         <v>504</v>
       </c>
       <c r="C406" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="D406">
+        <v>1</v>
       </c>
       <c r="E406" t="s">
-        <v>130</v>
+        <v>16</v>
       </c>
       <c r="F406" t="s">
         <v>17</v>
       </c>
       <c r="G406" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H406" t="s">
         <v>19</v>
@@ -10481,22 +10522,19 @@
         <v>504</v>
       </c>
       <c r="C407" t="s">
-        <v>14</v>
-      </c>
-      <c r="D407">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E407" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="F407" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G407" t="s">
+        <v>506</v>
+      </c>
+      <c r="H407" t="s">
         <v>19</v>
-      </c>
-      <c r="H407" t="s">
-        <v>507</v>
       </c>
       <c r="I407">
         <v>15244</v>
@@ -10516,22 +10554,22 @@
         <v>504</v>
       </c>
       <c r="C408" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D408">
         <v>1</v>
       </c>
       <c r="E408" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F408" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G408" t="s">
-        <v>508</v>
+        <v>19</v>
       </c>
       <c r="H408" t="s">
-        <v>19</v>
+        <v>507</v>
       </c>
       <c r="I408">
         <v>15244</v>
@@ -10557,24 +10595,24 @@
         <v>1</v>
       </c>
       <c r="E409" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F409" t="s">
         <v>17</v>
       </c>
       <c r="G409" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H409" t="s">
         <v>19</v>
       </c>
       <c r="I409">
-        <v>15103</v>
+        <v>15244</v>
       </c>
       <c r="J409">
-        <v>141</v>
-      </c>
-      <c r="L409" t="b">
+        <v>0</v>
+      </c>
+      <c r="L409" s="5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10586,34 +10624,31 @@
         <v>504</v>
       </c>
       <c r="C410" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D410">
         <v>1</v>
       </c>
       <c r="E410" t="s">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="F410" t="s">
-        <v>34</v>
-      </c>
-      <c r="G410" t="s">
-        <v>511</v>
+        <v>17</v>
+      </c>
+      <c r="G410" s="4" t="s">
+        <v>641</v>
       </c>
       <c r="H410" t="s">
-        <v>512</v>
+        <v>19</v>
       </c>
       <c r="I410">
-        <v>4217</v>
+        <v>15244</v>
       </c>
       <c r="J410">
-        <v>11027</v>
-      </c>
-      <c r="K410" t="s">
-        <v>513</v>
-      </c>
-      <c r="L410" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L410" s="5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.3">
@@ -10624,28 +10659,28 @@
         <v>504</v>
       </c>
       <c r="C411" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="D411">
         <v>1</v>
       </c>
       <c r="E411" t="s">
-        <v>514</v>
+        <v>30</v>
       </c>
       <c r="F411" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G411" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="H411" t="s">
-        <v>516</v>
+        <v>19</v>
       </c>
       <c r="I411">
-        <v>10184</v>
+        <v>15103</v>
       </c>
       <c r="J411">
-        <v>5060</v>
+        <v>141</v>
       </c>
       <c r="L411" t="b">
         <v>0</v>
@@ -10659,31 +10694,34 @@
         <v>504</v>
       </c>
       <c r="C412" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D412">
         <v>1</v>
       </c>
       <c r="E412" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="F412" t="s">
         <v>34</v>
       </c>
       <c r="G412" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="H412" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="I412">
-        <v>10202</v>
+        <v>4217</v>
       </c>
       <c r="J412">
-        <v>5042</v>
+        <v>11027</v>
+      </c>
+      <c r="K412" t="s">
+        <v>513</v>
       </c>
       <c r="L412" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.3">
@@ -10694,28 +10732,28 @@
         <v>504</v>
       </c>
       <c r="C413" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D413">
         <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F413" t="s">
         <v>34</v>
       </c>
       <c r="G413" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H413" t="s">
         <v>516</v>
       </c>
       <c r="I413">
-        <v>10200</v>
+        <v>10184</v>
       </c>
       <c r="J413">
-        <v>5044</v>
+        <v>5060</v>
       </c>
       <c r="L413" t="b">
         <v>0</v>
@@ -10735,7 +10773,7 @@
         <v>1</v>
       </c>
       <c r="E414" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F414" t="s">
         <v>34</v>
@@ -10747,10 +10785,10 @@
         <v>516</v>
       </c>
       <c r="I414">
-        <v>10197</v>
+        <v>10202</v>
       </c>
       <c r="J414">
-        <v>5047</v>
+        <v>5042</v>
       </c>
       <c r="L414" t="b">
         <v>0</v>
@@ -10764,13 +10802,13 @@
         <v>504</v>
       </c>
       <c r="C415" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="D415">
         <v>1</v>
       </c>
       <c r="E415" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F415" t="s">
         <v>34</v>
@@ -10782,10 +10820,10 @@
         <v>516</v>
       </c>
       <c r="I415">
-        <v>10195</v>
+        <v>10200</v>
       </c>
       <c r="J415">
-        <v>5049</v>
+        <v>5044</v>
       </c>
       <c r="L415" t="b">
         <v>0</v>
@@ -10799,28 +10837,28 @@
         <v>504</v>
       </c>
       <c r="C416" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="D416">
         <v>1</v>
       </c>
       <c r="E416" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F416" t="s">
         <v>34</v>
       </c>
       <c r="G416" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H416" t="s">
         <v>516</v>
       </c>
       <c r="I416">
-        <v>10193</v>
+        <v>10197</v>
       </c>
       <c r="J416">
-        <v>5051</v>
+        <v>5047</v>
       </c>
       <c r="L416" t="b">
         <v>0</v>
@@ -10834,28 +10872,28 @@
         <v>504</v>
       </c>
       <c r="C417" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="D417">
         <v>1</v>
       </c>
       <c r="E417" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F417" t="s">
         <v>34</v>
       </c>
       <c r="G417" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H417" t="s">
         <v>516</v>
       </c>
       <c r="I417">
-        <v>10210</v>
+        <v>10195</v>
       </c>
       <c r="J417">
-        <v>5034</v>
+        <v>5049</v>
       </c>
       <c r="L417" t="b">
         <v>0</v>
@@ -10875,22 +10913,22 @@
         <v>1</v>
       </c>
       <c r="E418" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F418" t="s">
         <v>34</v>
       </c>
       <c r="G418" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H418" t="s">
         <v>516</v>
       </c>
       <c r="I418">
-        <v>10263</v>
+        <v>10193</v>
       </c>
       <c r="J418">
-        <v>4981</v>
+        <v>5051</v>
       </c>
       <c r="L418" t="b">
         <v>0</v>
@@ -10904,28 +10942,28 @@
         <v>504</v>
       </c>
       <c r="C419" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="D419">
         <v>1</v>
       </c>
       <c r="E419" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F419" t="s">
         <v>34</v>
       </c>
       <c r="G419" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H419" t="s">
         <v>516</v>
       </c>
       <c r="I419">
-        <v>12120</v>
+        <v>10210</v>
       </c>
       <c r="J419">
-        <v>3124</v>
+        <v>5034</v>
       </c>
       <c r="L419" t="b">
         <v>0</v>
@@ -10939,28 +10977,28 @@
         <v>504</v>
       </c>
       <c r="C420" t="s">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="D420">
         <v>1</v>
       </c>
       <c r="E420" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F420" t="s">
         <v>34</v>
       </c>
       <c r="G420" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="H420" t="s">
         <v>516</v>
       </c>
       <c r="I420">
-        <v>10175</v>
+        <v>10263</v>
       </c>
       <c r="J420">
-        <v>5069</v>
+        <v>4981</v>
       </c>
       <c r="L420" t="b">
         <v>0</v>
@@ -10974,28 +11012,28 @@
         <v>504</v>
       </c>
       <c r="C421" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D421">
         <v>1</v>
       </c>
       <c r="E421" t="s">
-        <v>14</v>
+        <v>526</v>
       </c>
       <c r="F421" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G421" t="s">
-        <v>19</v>
+        <v>525</v>
       </c>
       <c r="H421" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="I421">
-        <v>15244</v>
+        <v>12120</v>
       </c>
       <c r="J421">
-        <v>0</v>
+        <v>3124</v>
       </c>
       <c r="L421" t="b">
         <v>0</v>
@@ -11003,34 +11041,34 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="B422" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="C422" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D422">
         <v>1</v>
       </c>
       <c r="E422" t="s">
-        <v>16</v>
+        <v>527</v>
       </c>
       <c r="F422" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G422" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="H422" t="s">
-        <v>19</v>
+        <v>516</v>
       </c>
       <c r="I422">
-        <v>6047</v>
+        <v>10175</v>
       </c>
       <c r="J422">
-        <v>0</v>
+        <v>5069</v>
       </c>
       <c r="L422" t="b">
         <v>0</v>
@@ -11038,28 +11076,31 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="B423" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="C423" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="D423">
+        <v>1</v>
       </c>
       <c r="E423" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F423" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G423" t="s">
-        <v>506</v>
+        <v>19</v>
       </c>
       <c r="H423" t="s">
-        <v>19</v>
+        <v>528</v>
       </c>
       <c r="I423">
-        <v>6047</v>
+        <v>15244</v>
       </c>
       <c r="J423">
         <v>0</v>
@@ -11082,16 +11123,16 @@
         <v>1</v>
       </c>
       <c r="E424" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F424" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G424" t="s">
+        <v>531</v>
+      </c>
+      <c r="H424" t="s">
         <v>19</v>
-      </c>
-      <c r="H424" t="s">
-        <v>532</v>
       </c>
       <c r="I424">
         <v>6047</v>
@@ -11111,19 +11152,16 @@
         <v>530</v>
       </c>
       <c r="C425" t="s">
-        <v>95</v>
-      </c>
-      <c r="D425">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E425" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="F425" t="s">
         <v>17</v>
       </c>
       <c r="G425" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="H425" t="s">
         <v>19</v>
@@ -11146,13 +11184,31 @@
         <v>530</v>
       </c>
       <c r="C426" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D426">
         <v>1</v>
       </c>
       <c r="E426" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="F426" t="s">
+        <v>22</v>
+      </c>
+      <c r="G426" t="s">
+        <v>19</v>
+      </c>
+      <c r="H426" t="s">
+        <v>532</v>
+      </c>
+      <c r="I426">
+        <v>6047</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+      <c r="L426" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.3">
@@ -11169,22 +11225,22 @@
         <v>1</v>
       </c>
       <c r="E427" t="s">
-        <v>534</v>
+        <v>28</v>
       </c>
       <c r="F427" t="s">
         <v>17</v>
       </c>
       <c r="G427" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H427" t="s">
         <v>19</v>
       </c>
       <c r="I427">
-        <v>6038</v>
+        <v>6047</v>
       </c>
       <c r="J427">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L427" t="b">
         <v>0</v>
@@ -11198,31 +11254,13 @@
         <v>530</v>
       </c>
       <c r="C428" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D428">
         <v>1</v>
       </c>
       <c r="E428" t="s">
-        <v>37</v>
-      </c>
-      <c r="F428" t="s">
-        <v>34</v>
-      </c>
-      <c r="G428" t="s">
-        <v>536</v>
-      </c>
-      <c r="H428" t="s">
-        <v>537</v>
-      </c>
-      <c r="I428">
-        <v>5919</v>
-      </c>
-      <c r="J428">
-        <v>128</v>
-      </c>
-      <c r="L428" t="b">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.3">
@@ -11233,28 +11271,28 @@
         <v>530</v>
       </c>
       <c r="C429" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="D429">
         <v>1</v>
       </c>
       <c r="E429" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F429" t="s">
         <v>17</v>
       </c>
       <c r="G429" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H429" t="s">
         <v>19</v>
       </c>
       <c r="I429">
-        <v>5860</v>
+        <v>6038</v>
       </c>
       <c r="J429">
-        <v>187</v>
+        <v>9</v>
       </c>
       <c r="L429" t="b">
         <v>0</v>
@@ -11268,28 +11306,28 @@
         <v>530</v>
       </c>
       <c r="C430" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D430">
         <v>1</v>
       </c>
       <c r="E430" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F430" t="s">
         <v>34</v>
       </c>
       <c r="G430" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H430" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="I430">
-        <v>6032</v>
+        <v>5919</v>
       </c>
       <c r="J430">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="L430" t="b">
         <v>0</v>
@@ -11303,28 +11341,28 @@
         <v>530</v>
       </c>
       <c r="C431" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D431">
         <v>1</v>
       </c>
       <c r="E431" t="s">
-        <v>40</v>
+        <v>538</v>
       </c>
       <c r="F431" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G431" t="s">
+        <v>539</v>
+      </c>
+      <c r="H431" t="s">
         <v>19</v>
       </c>
-      <c r="H431" t="s">
-        <v>542</v>
-      </c>
       <c r="I431">
-        <v>5900</v>
+        <v>5860</v>
       </c>
       <c r="J431">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="L431" t="b">
         <v>0</v>
@@ -11338,34 +11376,31 @@
         <v>530</v>
       </c>
       <c r="C432" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D432">
         <v>1</v>
       </c>
       <c r="E432" t="s">
-        <v>543</v>
+        <v>48</v>
       </c>
       <c r="F432" t="s">
         <v>34</v>
       </c>
       <c r="G432" t="s">
-        <v>19</v>
+        <v>540</v>
       </c>
       <c r="H432" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="I432">
-        <v>1512</v>
+        <v>6032</v>
       </c>
       <c r="J432">
-        <v>4535</v>
-      </c>
-      <c r="K432" t="s">
-        <v>513</v>
+        <v>15</v>
       </c>
       <c r="L432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
@@ -11376,28 +11411,28 @@
         <v>530</v>
       </c>
       <c r="C433" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D433">
         <v>1</v>
       </c>
       <c r="E433" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F433" t="s">
         <v>34</v>
       </c>
       <c r="G433" t="s">
-        <v>545</v>
+        <v>19</v>
       </c>
       <c r="H433" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="I433">
-        <v>5920</v>
+        <v>5900</v>
       </c>
       <c r="J433">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="L433" t="b">
         <v>0</v>
@@ -11411,31 +11446,34 @@
         <v>530</v>
       </c>
       <c r="C434" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="D434">
         <v>1</v>
       </c>
       <c r="E434" t="s">
-        <v>45</v>
+        <v>543</v>
       </c>
       <c r="F434" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G434" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="H434" t="s">
-        <v>19</v>
+        <v>544</v>
       </c>
       <c r="I434">
-        <v>5919</v>
+        <v>1512</v>
       </c>
       <c r="J434">
-        <v>128</v>
+        <v>4535</v>
+      </c>
+      <c r="K434" t="s">
+        <v>513</v>
       </c>
       <c r="L434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
@@ -11446,28 +11484,28 @@
         <v>530</v>
       </c>
       <c r="C435" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D435">
         <v>1</v>
       </c>
       <c r="E435" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F435" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G435" t="s">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="H435" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
       <c r="I435">
-        <v>6047</v>
+        <v>5920</v>
       </c>
       <c r="J435">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L435" t="b">
         <v>0</v>
@@ -11475,34 +11513,34 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="B436" t="s">
         <v>530</v>
       </c>
       <c r="C436" t="s">
-        <v>95</v>
-      </c>
-      <c r="D436" t="s">
-        <v>549</v>
+        <v>42</v>
+      </c>
+      <c r="D436">
+        <v>1</v>
       </c>
       <c r="E436" t="s">
-        <v>550</v>
+        <v>45</v>
       </c>
       <c r="F436" t="s">
         <v>17</v>
       </c>
       <c r="G436" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="H436" t="s">
         <v>19</v>
       </c>
       <c r="I436">
-        <v>6037</v>
+        <v>5919</v>
       </c>
       <c r="J436">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="L436" t="b">
         <v>0</v>
@@ -11510,34 +11548,34 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="B437" t="s">
         <v>530</v>
       </c>
       <c r="C437" t="s">
-        <v>32</v>
-      </c>
-      <c r="D437" t="s">
-        <v>549</v>
+        <v>14</v>
+      </c>
+      <c r="D437">
+        <v>1</v>
       </c>
       <c r="E437" t="s">
-        <v>551</v>
+        <v>14</v>
       </c>
       <c r="F437" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G437" t="s">
         <v>19</v>
       </c>
       <c r="H437" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I437">
-        <v>5860</v>
+        <v>6047</v>
       </c>
       <c r="J437">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="L437" t="b">
         <v>0</v>
@@ -11551,31 +11589,28 @@
         <v>530</v>
       </c>
       <c r="C438" t="s">
-        <v>162</v>
-      </c>
-      <c r="D438">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="D438" t="s">
+        <v>549</v>
       </c>
       <c r="E438" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F438" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G438" t="s">
+        <v>533</v>
+      </c>
+      <c r="H438" t="s">
         <v>19</v>
       </c>
-      <c r="H438" t="s">
-        <v>554</v>
-      </c>
       <c r="I438">
-        <v>4275</v>
+        <v>6037</v>
       </c>
       <c r="J438">
-        <v>1772</v>
-      </c>
-      <c r="K438" t="s">
-        <v>555</v>
+        <v>10</v>
       </c>
       <c r="L438" t="b">
         <v>0</v>
@@ -11589,13 +11624,13 @@
         <v>530</v>
       </c>
       <c r="C439" t="s">
-        <v>89</v>
-      </c>
-      <c r="D439">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="D439" t="s">
+        <v>549</v>
       </c>
       <c r="E439" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F439" t="s">
         <v>34</v>
@@ -11604,19 +11639,16 @@
         <v>19</v>
       </c>
       <c r="H439" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I439">
-        <v>3816</v>
+        <v>5860</v>
       </c>
       <c r="J439">
-        <v>2231</v>
-      </c>
-      <c r="K439" t="s">
-        <v>557</v>
+        <v>187</v>
       </c>
       <c r="L439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.3">
@@ -11627,34 +11659,34 @@
         <v>530</v>
       </c>
       <c r="C440" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="D440">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E440" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F440" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G440" t="s">
-        <v>559</v>
+        <v>19</v>
       </c>
       <c r="H440" t="s">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="I440">
-        <v>72</v>
+        <v>4275</v>
       </c>
       <c r="J440">
-        <v>5975</v>
+        <v>1772</v>
       </c>
       <c r="K440" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="L440" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.3">
@@ -11665,37 +11697,37 @@
         <v>530</v>
       </c>
       <c r="C441" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D441">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E441" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F441" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G441" t="s">
-        <v>562</v>
+        <v>19</v>
       </c>
       <c r="H441" t="s">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="I441">
-        <v>121</v>
+        <v>3816</v>
       </c>
       <c r="J441">
-        <v>5926</v>
+        <v>2231</v>
       </c>
       <c r="K441" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="L441" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>548</v>
       </c>
@@ -11709,22 +11741,22 @@
         <v>4</v>
       </c>
       <c r="E442" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="F442" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G442" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="H442" t="s">
-        <v>565</v>
+        <v>19</v>
       </c>
       <c r="I442">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="J442">
-        <v>6045</v>
+        <v>5975</v>
       </c>
       <c r="K442" t="s">
         <v>560</v>
@@ -11735,69 +11767,78 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="B443" t="s">
-        <v>69</v>
+        <v>530</v>
       </c>
       <c r="C443" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D443">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E443" t="s">
-        <v>16</v>
+        <v>561</v>
       </c>
       <c r="F443" t="s">
         <v>17</v>
       </c>
       <c r="G443" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="H443" t="s">
         <v>19</v>
       </c>
       <c r="I443">
-        <v>14337</v>
+        <v>121</v>
       </c>
       <c r="J443">
-        <v>0</v>
+        <v>5926</v>
+      </c>
+      <c r="K443" t="s">
+        <v>560</v>
       </c>
       <c r="L443" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="B444" t="s">
-        <v>69</v>
+        <v>530</v>
       </c>
       <c r="C444" t="s">
-        <v>24</v>
+        <v>42</v>
+      </c>
+      <c r="D444">
+        <v>4</v>
       </c>
       <c r="E444" t="s">
-        <v>130</v>
+        <v>563</v>
       </c>
       <c r="F444" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G444" t="s">
-        <v>506</v>
+        <v>564</v>
       </c>
       <c r="H444" t="s">
-        <v>19</v>
+        <v>565</v>
       </c>
       <c r="I444">
-        <v>14337</v>
+        <v>2</v>
       </c>
       <c r="J444">
-        <v>0</v>
+        <v>6045</v>
+      </c>
+      <c r="K444" t="s">
+        <v>560</v>
       </c>
       <c r="L444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.3">
@@ -11814,16 +11855,16 @@
         <v>1</v>
       </c>
       <c r="E445" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F445" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G445" t="s">
+        <v>531</v>
+      </c>
+      <c r="H445" t="s">
         <v>19</v>
-      </c>
-      <c r="H445" t="s">
-        <v>532</v>
       </c>
       <c r="I445">
         <v>14337</v>
@@ -11843,19 +11884,16 @@
         <v>69</v>
       </c>
       <c r="C446" t="s">
-        <v>95</v>
-      </c>
-      <c r="D446">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E446" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="F446" t="s">
         <v>17</v>
       </c>
       <c r="G446" t="s">
-        <v>567</v>
+        <v>506</v>
       </c>
       <c r="H446" t="s">
         <v>19</v>
@@ -11878,13 +11916,31 @@
         <v>69</v>
       </c>
       <c r="C447" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D447">
         <v>1</v>
       </c>
       <c r="E447" t="s">
-        <v>30</v>
+        <v>21</v>
+      </c>
+      <c r="F447" t="s">
+        <v>22</v>
+      </c>
+      <c r="G447" t="s">
+        <v>19</v>
+      </c>
+      <c r="H447" t="s">
+        <v>532</v>
+      </c>
+      <c r="I447">
+        <v>14337</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+      <c r="L447" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.3">
@@ -11901,22 +11957,22 @@
         <v>1</v>
       </c>
       <c r="E448" t="s">
-        <v>534</v>
+        <v>28</v>
       </c>
       <c r="F448" t="s">
         <v>17</v>
       </c>
       <c r="G448" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H448" t="s">
         <v>19</v>
       </c>
       <c r="I448">
-        <v>14320</v>
+        <v>14337</v>
       </c>
       <c r="J448">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L448" t="b">
         <v>0</v>
@@ -11930,31 +11986,13 @@
         <v>69</v>
       </c>
       <c r="C449" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D449">
         <v>1</v>
       </c>
       <c r="E449" t="s">
-        <v>569</v>
-      </c>
-      <c r="F449" t="s">
-        <v>34</v>
-      </c>
-      <c r="G449" t="s">
-        <v>19</v>
-      </c>
-      <c r="H449" t="s">
-        <v>570</v>
-      </c>
-      <c r="I449">
-        <v>14195</v>
-      </c>
-      <c r="J449">
-        <v>142</v>
-      </c>
-      <c r="L449" t="b">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.3">
@@ -11965,28 +12003,28 @@
         <v>69</v>
       </c>
       <c r="C450" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D450">
         <v>1</v>
       </c>
       <c r="E450" t="s">
-        <v>14</v>
+        <v>534</v>
       </c>
       <c r="F450" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G450" t="s">
+        <v>568</v>
+      </c>
+      <c r="H450" t="s">
         <v>19</v>
       </c>
-      <c r="H450" t="s">
-        <v>571</v>
-      </c>
       <c r="I450">
-        <v>14337</v>
+        <v>14320</v>
       </c>
       <c r="J450">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L450" t="b">
         <v>0</v>
@@ -12000,28 +12038,28 @@
         <v>69</v>
       </c>
       <c r="C451" t="s">
-        <v>95</v>
-      </c>
-      <c r="D451" t="s">
-        <v>549</v>
+        <v>69</v>
+      </c>
+      <c r="D451">
+        <v>1</v>
       </c>
       <c r="E451" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="F451" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G451" t="s">
-        <v>567</v>
+        <v>19</v>
       </c>
       <c r="H451" t="s">
-        <v>19</v>
+        <v>570</v>
       </c>
       <c r="I451">
-        <v>14319</v>
+        <v>14195</v>
       </c>
       <c r="J451">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="L451" t="b">
         <v>0</v>
@@ -12029,10 +12067,10 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B452" t="s">
-        <v>573</v>
+        <v>69</v>
       </c>
       <c r="C452" t="s">
         <v>14</v>
@@ -12041,19 +12079,19 @@
         <v>1</v>
       </c>
       <c r="E452" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F452" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G452" t="s">
-        <v>574</v>
+        <v>19</v>
       </c>
       <c r="H452" t="s">
-        <v>19</v>
+        <v>571</v>
       </c>
       <c r="I452">
-        <v>15242</v>
+        <v>14337</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -12064,31 +12102,34 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B453" t="s">
-        <v>573</v>
+        <v>69</v>
       </c>
       <c r="C453" t="s">
-        <v>24</v>
+        <v>95</v>
+      </c>
+      <c r="D453" t="s">
+        <v>549</v>
       </c>
       <c r="E453" t="s">
-        <v>130</v>
+        <v>550</v>
       </c>
       <c r="F453" t="s">
         <v>17</v>
       </c>
       <c r="G453" t="s">
-        <v>506</v>
+        <v>567</v>
       </c>
       <c r="H453" t="s">
         <v>19</v>
       </c>
       <c r="I453">
-        <v>15242</v>
+        <v>14319</v>
       </c>
       <c r="J453">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L453" t="b">
         <v>0</v>
@@ -12108,16 +12149,16 @@
         <v>1</v>
       </c>
       <c r="E454" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F454" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G454" t="s">
+        <v>574</v>
+      </c>
+      <c r="H454" t="s">
         <v>19</v>
-      </c>
-      <c r="H454" t="s">
-        <v>507</v>
       </c>
       <c r="I454">
         <v>15242</v>
@@ -12137,19 +12178,16 @@
         <v>573</v>
       </c>
       <c r="C455" t="s">
-        <v>95</v>
-      </c>
-      <c r="D455">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E455" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="F455" t="s">
         <v>17</v>
       </c>
       <c r="G455" t="s">
-        <v>575</v>
+        <v>506</v>
       </c>
       <c r="H455" t="s">
         <v>19</v>
@@ -12172,28 +12210,28 @@
         <v>573</v>
       </c>
       <c r="C456" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D456">
         <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F456" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G456" t="s">
-        <v>576</v>
+        <v>19</v>
       </c>
       <c r="H456" t="s">
-        <v>19</v>
+        <v>507</v>
       </c>
       <c r="I456">
-        <v>15144</v>
+        <v>15242</v>
       </c>
       <c r="J456">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L456" t="b">
         <v>0</v>
@@ -12207,13 +12245,31 @@
         <v>573</v>
       </c>
       <c r="C457" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D457">
         <v>1</v>
       </c>
       <c r="E457" t="s">
-        <v>577</v>
+        <v>28</v>
+      </c>
+      <c r="F457" t="s">
+        <v>17</v>
+      </c>
+      <c r="G457" t="s">
+        <v>575</v>
+      </c>
+      <c r="H457" t="s">
+        <v>19</v>
+      </c>
+      <c r="I457">
+        <v>15242</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
+      <c r="L457" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.3">
@@ -12224,13 +12280,31 @@
         <v>573</v>
       </c>
       <c r="C458" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D458">
         <v>1</v>
       </c>
       <c r="E458" t="s">
-        <v>578</v>
+        <v>30</v>
+      </c>
+      <c r="F458" t="s">
+        <v>17</v>
+      </c>
+      <c r="G458" t="s">
+        <v>576</v>
+      </c>
+      <c r="H458" t="s">
+        <v>19</v>
+      </c>
+      <c r="I458">
+        <v>15144</v>
+      </c>
+      <c r="J458">
+        <v>98</v>
+      </c>
+      <c r="L458" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.3">
@@ -12247,7 +12321,7 @@
         <v>1</v>
       </c>
       <c r="E459" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.3">
@@ -12264,7 +12338,7 @@
         <v>1</v>
       </c>
       <c r="E460" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.3">
@@ -12275,34 +12349,13 @@
         <v>573</v>
       </c>
       <c r="C461" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D461">
         <v>1</v>
       </c>
       <c r="E461" t="s">
-        <v>581</v>
-      </c>
-      <c r="F461" t="s">
-        <v>34</v>
-      </c>
-      <c r="G461" t="s">
-        <v>582</v>
-      </c>
-      <c r="H461" t="s">
-        <v>516</v>
-      </c>
-      <c r="I461">
-        <v>3868</v>
-      </c>
-      <c r="J461">
-        <v>11374</v>
-      </c>
-      <c r="K461" t="s">
-        <v>57</v>
-      </c>
-      <c r="L461" t="b">
-        <v>1</v>
+        <v>579</v>
       </c>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.3">
@@ -12313,34 +12366,13 @@
         <v>573</v>
       </c>
       <c r="C462" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D462">
         <v>1</v>
       </c>
       <c r="E462" t="s">
-        <v>583</v>
-      </c>
-      <c r="F462" t="s">
-        <v>34</v>
-      </c>
-      <c r="G462" t="s">
-        <v>584</v>
-      </c>
-      <c r="H462" t="s">
-        <v>516</v>
-      </c>
-      <c r="I462">
-        <v>3868</v>
-      </c>
-      <c r="J462">
-        <v>11374</v>
-      </c>
-      <c r="K462" t="s">
-        <v>57</v>
-      </c>
-      <c r="L462" t="b">
-        <v>1</v>
+        <v>580</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.3">
@@ -12357,13 +12389,13 @@
         <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F463" t="s">
         <v>34</v>
       </c>
       <c r="G463" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H463" t="s">
         <v>516</v>
@@ -12395,25 +12427,28 @@
         <v>1</v>
       </c>
       <c r="E464" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F464" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G464" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="H464" t="s">
-        <v>19</v>
+        <v>516</v>
       </c>
       <c r="I464">
-        <v>11770</v>
+        <v>3868</v>
       </c>
       <c r="J464">
-        <v>3472</v>
+        <v>11374</v>
+      </c>
+      <c r="K464" t="s">
+        <v>57</v>
       </c>
       <c r="L464" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.3">
@@ -12430,22 +12465,25 @@
         <v>1</v>
       </c>
       <c r="E465" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F465" t="s">
         <v>34</v>
       </c>
       <c r="G465" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="H465" t="s">
         <v>516</v>
       </c>
       <c r="I465">
-        <v>8517</v>
+        <v>3868</v>
       </c>
       <c r="J465">
-        <v>6725</v>
+        <v>11374</v>
+      </c>
+      <c r="K465" t="s">
+        <v>57</v>
       </c>
       <c r="L465" t="b">
         <v>1</v>
@@ -12465,25 +12503,25 @@
         <v>1</v>
       </c>
       <c r="E466" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="F466" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G466" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H466" t="s">
-        <v>516</v>
+        <v>19</v>
       </c>
       <c r="I466">
-        <v>8504</v>
+        <v>11770</v>
       </c>
       <c r="J466">
-        <v>6738</v>
+        <v>3472</v>
       </c>
       <c r="L466" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.3">
@@ -12500,22 +12538,22 @@
         <v>1</v>
       </c>
       <c r="E467" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F467" t="s">
         <v>34</v>
       </c>
       <c r="G467" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H467" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I467">
-        <v>8510</v>
+        <v>8517</v>
       </c>
       <c r="J467">
-        <v>6732</v>
+        <v>6725</v>
       </c>
       <c r="L467" t="b">
         <v>1</v>
@@ -12535,22 +12573,22 @@
         <v>1</v>
       </c>
       <c r="E468" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F468" t="s">
         <v>34</v>
       </c>
       <c r="G468" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H468" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I468">
-        <v>8516</v>
+        <v>8504</v>
       </c>
       <c r="J468">
-        <v>6726</v>
+        <v>6738</v>
       </c>
       <c r="L468" t="b">
         <v>1</v>
@@ -12570,16 +12608,16 @@
         <v>1</v>
       </c>
       <c r="E469" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F469" t="s">
         <v>34</v>
       </c>
       <c r="G469" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="H469" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I469">
         <v>8510</v>
@@ -12605,22 +12643,22 @@
         <v>1</v>
       </c>
       <c r="E470" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F470" t="s">
         <v>34</v>
       </c>
       <c r="G470" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="H470" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I470">
-        <v>8512</v>
+        <v>8516</v>
       </c>
       <c r="J470">
-        <v>6730</v>
+        <v>6726</v>
       </c>
       <c r="L470" t="b">
         <v>1</v>
@@ -12634,28 +12672,28 @@
         <v>573</v>
       </c>
       <c r="C471" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D471">
         <v>1</v>
       </c>
       <c r="E471" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F471" t="s">
         <v>34</v>
       </c>
       <c r="G471" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="H471" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I471">
-        <v>8552</v>
+        <v>8510</v>
       </c>
       <c r="J471">
-        <v>6690</v>
+        <v>6732</v>
       </c>
       <c r="L471" t="b">
         <v>1</v>
@@ -12675,25 +12713,25 @@
         <v>1</v>
       </c>
       <c r="E472" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F472" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G472" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="H472" t="s">
-        <v>19</v>
+        <v>516</v>
       </c>
       <c r="I472">
-        <v>10215</v>
+        <v>8512</v>
       </c>
       <c r="J472">
-        <v>5027</v>
+        <v>6730</v>
       </c>
       <c r="L472" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.3">
@@ -12710,25 +12748,22 @@
         <v>1</v>
       </c>
       <c r="E473" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F473" t="s">
         <v>34</v>
       </c>
       <c r="G473" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="H473" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I473">
-        <v>3868</v>
+        <v>8552</v>
       </c>
       <c r="J473">
-        <v>11374</v>
-      </c>
-      <c r="K473" t="s">
-        <v>57</v>
+        <v>6690</v>
       </c>
       <c r="L473" t="b">
         <v>1</v>
@@ -12748,7 +12783,25 @@
         <v>1</v>
       </c>
       <c r="E474" t="s">
-        <v>601</v>
+        <v>598</v>
+      </c>
+      <c r="F474" t="s">
+        <v>17</v>
+      </c>
+      <c r="G474" t="s">
+        <v>599</v>
+      </c>
+      <c r="H474" t="s">
+        <v>19</v>
+      </c>
+      <c r="I474">
+        <v>10215</v>
+      </c>
+      <c r="J474">
+        <v>5027</v>
+      </c>
+      <c r="L474" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.3">
@@ -12759,28 +12812,31 @@
         <v>573</v>
       </c>
       <c r="C475" t="s">
-        <v>162</v>
+        <v>89</v>
       </c>
       <c r="D475">
         <v>1</v>
       </c>
       <c r="E475" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F475" t="s">
         <v>34</v>
       </c>
       <c r="G475" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="H475" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I475">
-        <v>5546</v>
+        <v>3868</v>
       </c>
       <c r="J475">
-        <v>9696</v>
+        <v>11374</v>
+      </c>
+      <c r="K475" t="s">
+        <v>57</v>
       </c>
       <c r="L475" t="b">
         <v>1</v>
@@ -12800,28 +12856,7 @@
         <v>1</v>
       </c>
       <c r="E476" t="s">
-        <v>603</v>
-      </c>
-      <c r="F476" t="s">
-        <v>17</v>
-      </c>
-      <c r="G476" t="s">
-        <v>604</v>
-      </c>
-      <c r="H476" t="s">
-        <v>19</v>
-      </c>
-      <c r="I476">
-        <v>3868</v>
-      </c>
-      <c r="J476">
-        <v>11374</v>
-      </c>
-      <c r="K476" t="s">
-        <v>57</v>
-      </c>
-      <c r="L476" t="b">
-        <v>1</v>
+        <v>601</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.3">
@@ -12838,7 +12873,25 @@
         <v>1</v>
       </c>
       <c r="E477" t="s">
-        <v>605</v>
+        <v>602</v>
+      </c>
+      <c r="F477" t="s">
+        <v>34</v>
+      </c>
+      <c r="G477" t="s">
+        <v>597</v>
+      </c>
+      <c r="H477" t="s">
+        <v>537</v>
+      </c>
+      <c r="I477">
+        <v>5546</v>
+      </c>
+      <c r="J477">
+        <v>9696</v>
+      </c>
+      <c r="L477" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.3">
@@ -12855,25 +12908,28 @@
         <v>1</v>
       </c>
       <c r="E478" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F478" t="s">
         <v>17</v>
       </c>
       <c r="G478" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="H478" t="s">
         <v>19</v>
       </c>
       <c r="I478">
-        <v>10046</v>
+        <v>3868</v>
       </c>
       <c r="J478">
-        <v>5196</v>
+        <v>11374</v>
+      </c>
+      <c r="K478" t="s">
+        <v>57</v>
       </c>
       <c r="L478" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.3">
@@ -12890,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="E479" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.3">
@@ -12907,22 +12963,22 @@
         <v>1</v>
       </c>
       <c r="E480" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F480" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G480" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="H480" t="s">
-        <v>516</v>
+        <v>19</v>
       </c>
       <c r="I480">
-        <v>15098</v>
+        <v>10046</v>
       </c>
       <c r="J480">
-        <v>144</v>
+        <v>5196</v>
       </c>
       <c r="L480" t="b">
         <v>0</v>
@@ -12942,28 +12998,7 @@
         <v>1</v>
       </c>
       <c r="E481" t="s">
-        <v>610</v>
-      </c>
-      <c r="F481" t="s">
-        <v>34</v>
-      </c>
-      <c r="G481" t="s">
-        <v>611</v>
-      </c>
-      <c r="H481" t="s">
-        <v>612</v>
-      </c>
-      <c r="I481">
-        <v>3868</v>
-      </c>
-      <c r="J481">
-        <v>11374</v>
-      </c>
-      <c r="K481" t="s">
-        <v>57</v>
-      </c>
-      <c r="L481" t="b">
-        <v>1</v>
+        <v>608</v>
       </c>
     </row>
     <row r="482" spans="1:12" x14ac:dyDescent="0.3">
@@ -12980,28 +13015,25 @@
         <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="F482" t="s">
         <v>34</v>
       </c>
       <c r="G482" t="s">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="H482" t="s">
-        <v>612</v>
+        <v>516</v>
       </c>
       <c r="I482">
-        <v>3868</v>
+        <v>15098</v>
       </c>
       <c r="J482">
-        <v>11374</v>
-      </c>
-      <c r="K482" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="L482" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.3">
@@ -13018,16 +13050,16 @@
         <v>1</v>
       </c>
       <c r="E483" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F483" t="s">
         <v>34</v>
       </c>
       <c r="G483" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="H483" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="I483">
         <v>3868</v>
@@ -13056,16 +13088,16 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="F484" t="s">
         <v>34</v>
       </c>
       <c r="G484" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="H484" t="s">
-        <v>516</v>
+        <v>612</v>
       </c>
       <c r="I484">
         <v>3868</v>
@@ -13094,22 +13126,25 @@
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F485" t="s">
         <v>34</v>
       </c>
       <c r="G485" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="H485" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="I485">
-        <v>3912</v>
+        <v>3868</v>
       </c>
       <c r="J485">
-        <v>11330</v>
+        <v>11374</v>
+      </c>
+      <c r="K485" t="s">
+        <v>57</v>
       </c>
       <c r="L485" t="b">
         <v>1</v>
@@ -13123,22 +13158,22 @@
         <v>573</v>
       </c>
       <c r="C486" t="s">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="D486">
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="F486" t="s">
         <v>34</v>
       </c>
       <c r="G486" t="s">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="H486" t="s">
-        <v>624</v>
+        <v>516</v>
       </c>
       <c r="I486">
         <v>3868</v>
@@ -13161,31 +13196,31 @@
         <v>573</v>
       </c>
       <c r="C487" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D487">
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>14</v>
+        <v>619</v>
       </c>
       <c r="F487" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G487" t="s">
-        <v>19</v>
+        <v>620</v>
       </c>
       <c r="H487" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="I487">
-        <v>15242</v>
+        <v>3912</v>
       </c>
       <c r="J487">
-        <v>0</v>
+        <v>11330</v>
       </c>
       <c r="L487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.3">
@@ -13196,31 +13231,34 @@
         <v>573</v>
       </c>
       <c r="C488" t="s">
-        <v>95</v>
-      </c>
-      <c r="D488" t="s">
-        <v>549</v>
+        <v>89</v>
+      </c>
+      <c r="D488">
+        <v>1</v>
       </c>
       <c r="E488" t="s">
-        <v>550</v>
+        <v>622</v>
       </c>
       <c r="F488" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G488" t="s">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="H488" t="s">
-        <v>19</v>
+        <v>624</v>
       </c>
       <c r="I488">
-        <v>15227</v>
+        <v>3868</v>
       </c>
       <c r="J488">
-        <v>15</v>
+        <v>11374</v>
+      </c>
+      <c r="K488" t="s">
+        <v>57</v>
       </c>
       <c r="L488" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.3">
@@ -13231,31 +13269,31 @@
         <v>573</v>
       </c>
       <c r="C489" t="s">
-        <v>162</v>
-      </c>
-      <c r="D489" t="s">
-        <v>549</v>
+        <v>14</v>
+      </c>
+      <c r="D489">
+        <v>1</v>
       </c>
       <c r="E489" t="s">
-        <v>626</v>
+        <v>14</v>
       </c>
       <c r="F489" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G489" t="s">
-        <v>511</v>
+        <v>19</v>
       </c>
       <c r="H489" t="s">
-        <v>512</v>
+        <v>625</v>
       </c>
       <c r="I489">
-        <v>5639</v>
+        <v>15242</v>
       </c>
       <c r="J489">
-        <v>9603</v>
+        <v>0</v>
       </c>
       <c r="L489" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.3">
@@ -13266,34 +13304,31 @@
         <v>573</v>
       </c>
       <c r="C490" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="D490" t="s">
         <v>549</v>
       </c>
       <c r="E490" t="s">
-        <v>627</v>
+        <v>550</v>
       </c>
       <c r="F490" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G490" t="s">
-        <v>628</v>
+        <v>575</v>
       </c>
       <c r="H490" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="I490">
-        <v>1772</v>
+        <v>15227</v>
       </c>
       <c r="J490">
-        <v>13470</v>
-      </c>
-      <c r="K490" t="s">
-        <v>555</v>
+        <v>15</v>
       </c>
       <c r="L490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.3">
@@ -13310,28 +13345,25 @@
         <v>549</v>
       </c>
       <c r="E491" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F491" t="s">
         <v>34</v>
       </c>
       <c r="G491" t="s">
-        <v>630</v>
+        <v>511</v>
       </c>
       <c r="H491" t="s">
-        <v>631</v>
+        <v>512</v>
       </c>
       <c r="I491">
-        <v>10759</v>
+        <v>5639</v>
       </c>
       <c r="J491">
-        <v>4483</v>
-      </c>
-      <c r="K491" t="s">
-        <v>557</v>
+        <v>9603</v>
       </c>
       <c r="L491" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.3">
@@ -13342,13 +13374,34 @@
         <v>573</v>
       </c>
       <c r="C492" t="s">
-        <v>89</v>
-      </c>
-      <c r="D492">
-        <v>2</v>
+        <v>162</v>
+      </c>
+      <c r="D492" t="s">
+        <v>549</v>
       </c>
       <c r="E492" t="s">
-        <v>632</v>
+        <v>627</v>
+      </c>
+      <c r="F492" t="s">
+        <v>34</v>
+      </c>
+      <c r="G492" t="s">
+        <v>628</v>
+      </c>
+      <c r="H492" t="s">
+        <v>136</v>
+      </c>
+      <c r="I492">
+        <v>1772</v>
+      </c>
+      <c r="J492">
+        <v>13470</v>
+      </c>
+      <c r="K492" t="s">
+        <v>555</v>
+      </c>
+      <c r="L492" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.3">
@@ -13359,28 +13412,31 @@
         <v>573</v>
       </c>
       <c r="C493" t="s">
-        <v>89</v>
-      </c>
-      <c r="D493">
-        <v>3</v>
+        <v>162</v>
+      </c>
+      <c r="D493" t="s">
+        <v>549</v>
       </c>
       <c r="E493" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F493" t="s">
         <v>34</v>
       </c>
       <c r="G493" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="H493" t="s">
-        <v>152</v>
+        <v>631</v>
       </c>
       <c r="I493">
-        <v>15203</v>
+        <v>10759</v>
       </c>
       <c r="J493">
-        <v>39</v>
+        <v>4483</v>
+      </c>
+      <c r="K493" t="s">
+        <v>557</v>
       </c>
       <c r="L493" t="b">
         <v>0</v>
@@ -13393,32 +13449,85 @@
       <c r="B494" t="s">
         <v>573</v>
       </c>
+      <c r="C494" t="s">
+        <v>89</v>
+      </c>
       <c r="D494">
+        <v>2</v>
+      </c>
+      <c r="E494" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A495" t="s">
+        <v>572</v>
+      </c>
+      <c r="B495" t="s">
+        <v>573</v>
+      </c>
+      <c r="C495" t="s">
+        <v>89</v>
+      </c>
+      <c r="D495">
+        <v>3</v>
+      </c>
+      <c r="E495" t="s">
+        <v>633</v>
+      </c>
+      <c r="F495" t="s">
+        <v>34</v>
+      </c>
+      <c r="G495" t="s">
+        <v>634</v>
+      </c>
+      <c r="H495" t="s">
+        <v>152</v>
+      </c>
+      <c r="I495">
+        <v>15203</v>
+      </c>
+      <c r="J495">
+        <v>39</v>
+      </c>
+      <c r="L495" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A496" t="s">
+        <v>572</v>
+      </c>
+      <c r="B496" t="s">
+        <v>573</v>
+      </c>
+      <c r="D496">
         <v>4</v>
       </c>
-      <c r="E494" t="s">
+      <c r="E496" t="s">
         <v>635</v>
       </c>
-      <c r="F494" t="s">
+      <c r="F496" t="s">
         <v>22</v>
       </c>
-      <c r="G494" t="s">
+      <c r="G496" t="s">
         <v>19</v>
       </c>
-      <c r="H494" t="s">
+      <c r="H496" t="s">
         <v>636</v>
       </c>
-      <c r="I494">
+      <c r="I496">
         <v>15242</v>
       </c>
-      <c r="J494">
-        <v>0</v>
-      </c>
-      <c r="L494" t="b">
+      <c r="J496">
+        <v>0</v>
+      </c>
+      <c r="L496" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_7DD945CF15660E0F62355476585DCE3A8742D602" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B768188C-54F6-4860-AE59-1D44E00C6C65}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_7DD945CF15660E0F62355476585DCE3A8742D602" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16647D70-D90C-4449-9EEE-EAE032D8937D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-3705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1962,6 +1975,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1989,20 +2016,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2021,11 +2034,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}" name="Tabella1" displayName="Tabella1" ref="A1:K487" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}" name="Tabella1" displayName="Tabella1" ref="A1:K487" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:K487" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="visit"/>
+        <filter val="BLCHANGE"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2333,6 +2346,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K487"/>
   <sheetFormatPr defaultColWidth="25.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="8" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2465,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2497,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3300,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3844,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>121</v>
       </c>
@@ -3876,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -4077,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -4306,7 +4322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>154</v>
       </c>
@@ -4390,7 +4406,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -4586,7 +4602,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>154</v>
       </c>
@@ -4642,7 +4658,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>154</v>
       </c>
@@ -4656,7 +4672,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>154</v>
       </c>
@@ -4754,7 +4770,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>154</v>
       </c>
@@ -4768,7 +4784,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>154</v>
       </c>
@@ -4894,7 +4910,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>154</v>
       </c>
@@ -9084,7 +9100,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>501</v>
       </c>
@@ -9113,7 +9129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>501</v>
       </c>
@@ -9142,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>501</v>
       </c>
@@ -9258,7 +9274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>501</v>
       </c>
@@ -9293,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>501</v>
       </c>
@@ -9325,7 +9341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>501</v>
       </c>
@@ -9357,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>501</v>
       </c>
@@ -9389,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>501</v>
       </c>
@@ -9421,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>501</v>
       </c>
@@ -9453,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>501</v>
       </c>
@@ -9485,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>501</v>
       </c>
@@ -9517,7 +9533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>501</v>
       </c>
@@ -9549,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>501</v>
       </c>
@@ -9581,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>501</v>
       </c>
@@ -9613,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>501</v>
       </c>
@@ -9729,7 +9745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>529</v>
       </c>
@@ -9758,7 +9774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>529</v>
       </c>
@@ -9772,7 +9788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>529</v>
       </c>
@@ -10045,7 +10061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>548</v>
       </c>
@@ -10353,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>564</v>
       </c>
@@ -10382,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>564</v>
       </c>
@@ -10396,7 +10412,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>564</v>
       </c>
@@ -10483,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>564</v>
       </c>
@@ -10608,7 +10624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>570</v>
       </c>
@@ -10640,7 +10656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>570</v>
       </c>
@@ -11470,7 +11486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>570</v>
       </c>

--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_7DD945CF15660E0F62355476585DCE3A8742D602" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16647D70-D90C-4449-9EEE-EAE032D8937D}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_7DD945CF15660E0F62355476585DCE3A8742D602" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F8174E-5949-4130-A936-60B80E04022D}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-3705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2035,13 +2035,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}" name="Tabella1" displayName="Tabella1" ref="A1:K487" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:K487" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BLCHANGE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K487" xr:uid="{E63766A8-0837-4848-AAF2-CB2948CF75CA}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{2DD95BA9-1A58-4558-BABE-1BC136183262}" name="file_name"/>
     <tableColumn id="2" xr3:uid="{DD74AB91-ABD2-432A-9E15-61C6BEBC4616}" name="file_code"/>
@@ -2347,7 +2341,11 @@
   <dimension ref="A1:K487"/>
   <sheetFormatPr defaultColWidth="25.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="76.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -2385,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2417,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2449,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2481,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2513,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2545,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2577,7 +2575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2609,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2641,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2673,7 +2671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2705,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2737,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2772,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2804,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2836,7 +2834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2868,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2900,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2932,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2964,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2996,7 +2994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -3028,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -3060,7 +3058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3092,7 +3090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3124,7 +3122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3156,7 +3154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3188,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3220,7 +3218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3252,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3284,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3316,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3348,7 +3346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3380,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3412,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3444,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3476,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3508,7 +3506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3540,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -3572,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -3604,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -3636,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -3668,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -3700,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3732,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -3764,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -3796,7 +3794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>121</v>
       </c>
@@ -3828,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -3860,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>121</v>
       </c>
@@ -3892,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -3924,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>121</v>
       </c>
@@ -3956,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>121</v>
       </c>
@@ -3991,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>121</v>
       </c>
@@ -4026,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>121</v>
       </c>
@@ -4061,7 +4059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>121</v>
       </c>
@@ -4093,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>121</v>
       </c>
@@ -4125,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>121</v>
       </c>
@@ -4139,7 +4137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>121</v>
       </c>
@@ -4153,7 +4151,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>121</v>
       </c>
@@ -4167,7 +4165,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>121</v>
       </c>
@@ -4181,7 +4179,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -4213,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -4227,7 +4225,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>121</v>
       </c>
@@ -4262,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>121</v>
       </c>
@@ -4294,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -4308,7 +4306,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>154</v>
       </c>
@@ -4322,7 +4320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>154</v>
       </c>
@@ -4336,7 +4334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -4350,7 +4348,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>154</v>
       </c>
@@ -4364,7 +4362,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>154</v>
       </c>
@@ -4378,7 +4376,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>154</v>
       </c>
@@ -4392,7 +4390,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>154</v>
       </c>
@@ -4406,7 +4404,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -4420,7 +4418,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>154</v>
       </c>
@@ -4434,7 +4432,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>154</v>
       </c>
@@ -4448,7 +4446,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>154</v>
       </c>
@@ -4462,7 +4460,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>154</v>
       </c>
@@ -4476,7 +4474,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>154</v>
       </c>
@@ -4490,7 +4488,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -4504,7 +4502,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -4518,7 +4516,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -4532,7 +4530,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>154</v>
       </c>
@@ -4546,7 +4544,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>154</v>
       </c>
@@ -4560,7 +4558,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>154</v>
       </c>
@@ -4574,7 +4572,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>154</v>
       </c>
@@ -4588,7 +4586,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>154</v>
       </c>
@@ -4602,7 +4600,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>154</v>
       </c>
@@ -4616,7 +4614,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>154</v>
       </c>
@@ -4630,7 +4628,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>154</v>
       </c>
@@ -4644,7 +4642,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>154</v>
       </c>
@@ -4658,7 +4656,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>154</v>
       </c>
@@ -4672,7 +4670,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>154</v>
       </c>
@@ -4686,7 +4684,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>154</v>
       </c>
@@ -4700,7 +4698,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>154</v>
       </c>
@@ -4714,7 +4712,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>154</v>
       </c>
@@ -4728,7 +4726,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>154</v>
       </c>
@@ -4742,7 +4740,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>154</v>
       </c>
@@ -4756,7 +4754,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>154</v>
       </c>
@@ -4770,7 +4768,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>154</v>
       </c>
@@ -4784,7 +4782,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>154</v>
       </c>
@@ -4798,7 +4796,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>154</v>
       </c>
@@ -4812,7 +4810,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>154</v>
       </c>
@@ -4826,7 +4824,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>154</v>
       </c>
@@ -4840,7 +4838,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>154</v>
       </c>
@@ -4854,7 +4852,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -4868,7 +4866,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>154</v>
       </c>
@@ -4882,7 +4880,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>154</v>
       </c>
@@ -4896,7 +4894,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>154</v>
       </c>
@@ -4910,7 +4908,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>154</v>
       </c>
@@ -4924,7 +4922,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>199</v>
       </c>
@@ -4956,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>199</v>
       </c>
@@ -4970,7 +4968,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>199</v>
       </c>
@@ -4984,7 +4982,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>199</v>
       </c>
@@ -4998,7 +4996,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>199</v>
       </c>
@@ -5012,7 +5010,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>199</v>
       </c>
@@ -5026,7 +5024,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>199</v>
       </c>
@@ -5040,7 +5038,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>199</v>
       </c>
@@ -5054,7 +5052,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>199</v>
       </c>
@@ -5068,7 +5066,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>199</v>
       </c>
@@ -5082,7 +5080,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>199</v>
       </c>
@@ -5096,7 +5094,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>199</v>
       </c>
@@ -5110,7 +5108,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>199</v>
       </c>
@@ -5124,7 +5122,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>199</v>
       </c>
@@ -5138,7 +5136,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>199</v>
       </c>
@@ -5152,7 +5150,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>199</v>
       </c>
@@ -5166,7 +5164,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>199</v>
       </c>
@@ -5180,7 +5178,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>199</v>
       </c>
@@ -5194,7 +5192,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>199</v>
       </c>
@@ -5208,7 +5206,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>199</v>
       </c>
@@ -5222,7 +5220,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>199</v>
       </c>
@@ -5236,7 +5234,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>199</v>
       </c>
@@ -5250,7 +5248,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>199</v>
       </c>
@@ -5264,7 +5262,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>199</v>
       </c>
@@ -5278,7 +5276,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>199</v>
       </c>
@@ -5292,7 +5290,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>199</v>
       </c>
@@ -5306,7 +5304,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>199</v>
       </c>
@@ -5320,7 +5318,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>199</v>
       </c>
@@ -5334,7 +5332,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>199</v>
       </c>
@@ -5348,7 +5346,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>199</v>
       </c>
@@ -5362,7 +5360,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>199</v>
       </c>
@@ -5376,7 +5374,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>199</v>
       </c>
@@ -5390,7 +5388,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>199</v>
       </c>
@@ -5404,7 +5402,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>199</v>
       </c>
@@ -5418,7 +5416,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>199</v>
       </c>
@@ -5432,7 +5430,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>199</v>
       </c>
@@ -5446,7 +5444,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>199</v>
       </c>
@@ -5460,7 +5458,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>199</v>
       </c>
@@ -5474,7 +5472,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>199</v>
       </c>
@@ -5488,7 +5486,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>199</v>
       </c>
@@ -5502,7 +5500,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>199</v>
       </c>
@@ -5516,7 +5514,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>199</v>
       </c>
@@ -5530,7 +5528,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>199</v>
       </c>
@@ -5544,7 +5542,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>199</v>
       </c>
@@ -5558,7 +5556,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>199</v>
       </c>
@@ -5572,7 +5570,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>199</v>
       </c>
@@ -5586,7 +5584,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -5600,7 +5598,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>199</v>
       </c>
@@ -5614,7 +5612,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>199</v>
       </c>
@@ -5628,7 +5626,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>199</v>
       </c>
@@ -5642,7 +5640,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>199</v>
       </c>
@@ -5656,7 +5654,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>199</v>
       </c>
@@ -5670,7 +5668,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>199</v>
       </c>
@@ -5684,7 +5682,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>199</v>
       </c>
@@ -5698,7 +5696,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>199</v>
       </c>
@@ -5712,7 +5710,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>199</v>
       </c>
@@ -5726,7 +5724,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -5740,7 +5738,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -5754,7 +5752,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -5768,7 +5766,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -5782,7 +5780,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>199</v>
       </c>
@@ -5796,7 +5794,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>199</v>
       </c>
@@ -5810,7 +5808,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>199</v>
       </c>
@@ -5824,7 +5822,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -5838,7 +5836,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>199</v>
       </c>
@@ -5852,7 +5850,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>199</v>
       </c>
@@ -5866,7 +5864,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>199</v>
       </c>
@@ -5880,7 +5878,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>199</v>
       </c>
@@ -5894,7 +5892,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>199</v>
       </c>
@@ -5908,7 +5906,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>199</v>
       </c>
@@ -5922,7 +5920,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -5936,7 +5934,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>199</v>
       </c>
@@ -5950,7 +5948,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>199</v>
       </c>
@@ -5964,7 +5962,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>199</v>
       </c>
@@ -5978,7 +5976,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>199</v>
       </c>
@@ -5992,7 +5990,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>199</v>
       </c>
@@ -6006,7 +6004,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>199</v>
       </c>
@@ -6020,7 +6018,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>199</v>
       </c>
@@ -6034,7 +6032,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>199</v>
       </c>
@@ -6048,7 +6046,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>199</v>
       </c>
@@ -6062,7 +6060,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>199</v>
       </c>
@@ -6076,7 +6074,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -6090,7 +6088,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -6104,7 +6102,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -6118,7 +6116,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>199</v>
       </c>
@@ -6132,7 +6130,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>199</v>
       </c>
@@ -6146,7 +6144,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -6160,7 +6158,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -6174,7 +6172,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -6188,7 +6186,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -6202,7 +6200,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -6216,7 +6214,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -6230,7 +6228,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -6244,7 +6242,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>199</v>
       </c>
@@ -6258,7 +6256,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -6272,7 +6270,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>199</v>
       </c>
@@ -6286,7 +6284,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>199</v>
       </c>
@@ -6300,7 +6298,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>199</v>
       </c>
@@ -6314,7 +6312,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>199</v>
       </c>
@@ -6328,7 +6326,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>199</v>
       </c>
@@ -6342,7 +6340,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>199</v>
       </c>
@@ -6356,7 +6354,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>199</v>
       </c>
@@ -6370,7 +6368,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>199</v>
       </c>
@@ -6384,7 +6382,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>199</v>
       </c>
@@ -6398,7 +6396,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>199</v>
       </c>
@@ -6412,7 +6410,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -6426,7 +6424,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>199</v>
       </c>
@@ -6440,7 +6438,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>199</v>
       </c>
@@ -6454,7 +6452,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>199</v>
       </c>
@@ -6468,7 +6466,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>199</v>
       </c>
@@ -6482,7 +6480,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>199</v>
       </c>
@@ -6496,7 +6494,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>199</v>
       </c>
@@ -6510,7 +6508,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>199</v>
       </c>
@@ -6524,7 +6522,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>199</v>
       </c>
@@ -6538,7 +6536,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>199</v>
       </c>
@@ -6552,7 +6550,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>199</v>
       </c>
@@ -6566,7 +6564,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>199</v>
       </c>
@@ -6580,7 +6578,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>199</v>
       </c>
@@ -6594,7 +6592,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>199</v>
       </c>
@@ -6608,7 +6606,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>199</v>
       </c>
@@ -6622,7 +6620,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>199</v>
       </c>
@@ -6636,7 +6634,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>199</v>
       </c>
@@ -6650,7 +6648,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>199</v>
       </c>
@@ -6664,7 +6662,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>199</v>
       </c>
@@ -6678,7 +6676,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>199</v>
       </c>
@@ -6692,7 +6690,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>199</v>
       </c>
@@ -6706,7 +6704,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>199</v>
       </c>
@@ -6720,7 +6718,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>199</v>
       </c>
@@ -6734,7 +6732,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>199</v>
       </c>
@@ -6748,7 +6746,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>199</v>
       </c>
@@ -6762,7 +6760,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>199</v>
       </c>
@@ -6776,7 +6774,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>199</v>
       </c>
@@ -6790,7 +6788,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>199</v>
       </c>
@@ -6804,7 +6802,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>199</v>
       </c>
@@ -6818,7 +6816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>199</v>
       </c>
@@ -6832,7 +6830,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>199</v>
       </c>
@@ -6846,7 +6844,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>199</v>
       </c>
@@ -6860,7 +6858,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>199</v>
       </c>
@@ -6874,7 +6872,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>199</v>
       </c>
@@ -6888,7 +6886,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>199</v>
       </c>
@@ -6902,7 +6900,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>199</v>
       </c>
@@ -6916,7 +6914,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>199</v>
       </c>
@@ -6930,7 +6928,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>199</v>
       </c>
@@ -6944,7 +6942,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>199</v>
       </c>
@@ -6958,7 +6956,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>199</v>
       </c>
@@ -6972,7 +6970,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>199</v>
       </c>
@@ -6986,7 +6984,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>199</v>
       </c>
@@ -7000,7 +6998,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>199</v>
       </c>
@@ -7014,7 +7012,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>199</v>
       </c>
@@ -7028,7 +7026,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>199</v>
       </c>
@@ -7042,7 +7040,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>199</v>
       </c>
@@ -7056,7 +7054,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>199</v>
       </c>
@@ -7070,7 +7068,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>199</v>
       </c>
@@ -7084,7 +7082,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>199</v>
       </c>
@@ -7098,7 +7096,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>199</v>
       </c>
@@ -7112,7 +7110,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>199</v>
       </c>
@@ -7126,7 +7124,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>199</v>
       </c>
@@ -7140,7 +7138,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>199</v>
       </c>
@@ -7154,7 +7152,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>199</v>
       </c>
@@ -7168,7 +7166,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>199</v>
       </c>
@@ -7182,7 +7180,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>199</v>
       </c>
@@ -7196,7 +7194,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>199</v>
       </c>
@@ -7210,7 +7208,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>199</v>
       </c>
@@ -7224,7 +7222,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>199</v>
       </c>
@@ -7238,7 +7236,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>199</v>
       </c>
@@ -7252,7 +7250,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>199</v>
       </c>
@@ -7266,7 +7264,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>199</v>
       </c>
@@ -7280,7 +7278,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>199</v>
       </c>
@@ -7294,7 +7292,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>199</v>
       </c>
@@ -7308,7 +7306,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>199</v>
       </c>
@@ -7322,7 +7320,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>199</v>
       </c>
@@ -7336,7 +7334,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>199</v>
       </c>
@@ -7350,7 +7348,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>199</v>
       </c>
@@ -7364,7 +7362,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>199</v>
       </c>
@@ -7378,7 +7376,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>199</v>
       </c>
@@ -7392,7 +7390,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>199</v>
       </c>
@@ -7406,7 +7404,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>199</v>
       </c>
@@ -7420,7 +7418,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>199</v>
       </c>
@@ -7434,7 +7432,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>199</v>
       </c>
@@ -7448,7 +7446,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>199</v>
       </c>
@@ -7462,7 +7460,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>199</v>
       </c>
@@ -7476,7 +7474,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>199</v>
       </c>
@@ -7490,7 +7488,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>199</v>
       </c>
@@ -7504,7 +7502,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>199</v>
       </c>
@@ -7518,7 +7516,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>199</v>
       </c>
@@ -7532,7 +7530,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>199</v>
       </c>
@@ -7546,7 +7544,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>199</v>
       </c>
@@ -7560,7 +7558,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>199</v>
       </c>
@@ -7574,7 +7572,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>199</v>
       </c>
@@ -7588,7 +7586,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>199</v>
       </c>
@@ -7602,7 +7600,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>199</v>
       </c>
@@ -7616,7 +7614,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>199</v>
       </c>
@@ -7630,7 +7628,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>199</v>
       </c>
@@ -7644,7 +7642,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>199</v>
       </c>
@@ -7658,7 +7656,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>199</v>
       </c>
@@ -7672,7 +7670,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>199</v>
       </c>
@@ -7686,7 +7684,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>199</v>
       </c>
@@ -7700,7 +7698,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>199</v>
       </c>
@@ -7714,7 +7712,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>199</v>
       </c>
@@ -7728,7 +7726,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>199</v>
       </c>
@@ -7742,7 +7740,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>199</v>
       </c>
@@ -7756,7 +7754,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>199</v>
       </c>
@@ -7770,7 +7768,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>199</v>
       </c>
@@ -7784,7 +7782,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>199</v>
       </c>
@@ -7798,7 +7796,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>199</v>
       </c>
@@ -7812,7 +7810,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>199</v>
       </c>
@@ -7826,7 +7824,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>199</v>
       </c>
@@ -7840,7 +7838,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>199</v>
       </c>
@@ -7854,7 +7852,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>199</v>
       </c>
@@ -7868,7 +7866,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>199</v>
       </c>
@@ -7882,7 +7880,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>199</v>
       </c>
@@ -7896,7 +7894,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>199</v>
       </c>
@@ -7910,7 +7908,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>199</v>
       </c>
@@ -7924,7 +7922,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>199</v>
       </c>
@@ -7938,7 +7936,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>199</v>
       </c>
@@ -7952,7 +7950,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>199</v>
       </c>
@@ -7966,7 +7964,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>199</v>
       </c>
@@ -7980,7 +7978,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>199</v>
       </c>
@@ -7994,7 +7992,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>199</v>
       </c>
@@ -8008,7 +8006,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>199</v>
       </c>
@@ -8022,7 +8020,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>199</v>
       </c>
@@ -8036,7 +8034,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>199</v>
       </c>
@@ -8050,7 +8048,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>199</v>
       </c>
@@ -8064,7 +8062,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>199</v>
       </c>
@@ -8078,7 +8076,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>199</v>
       </c>
@@ -8092,7 +8090,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>199</v>
       </c>
@@ -8106,7 +8104,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>199</v>
       </c>
@@ -8120,7 +8118,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>199</v>
       </c>
@@ -8134,7 +8132,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>199</v>
       </c>
@@ -8148,7 +8146,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>199</v>
       </c>
@@ -8162,7 +8160,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>199</v>
       </c>
@@ -8176,7 +8174,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>199</v>
       </c>
@@ -8190,7 +8188,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>199</v>
       </c>
@@ -8204,7 +8202,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>199</v>
       </c>
@@ -8218,7 +8216,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>199</v>
       </c>
@@ -8232,7 +8230,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>199</v>
       </c>
@@ -8246,7 +8244,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>199</v>
       </c>
@@ -8260,7 +8258,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>199</v>
       </c>
@@ -8274,7 +8272,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>199</v>
       </c>
@@ -8288,7 +8286,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>199</v>
       </c>
@@ -8302,7 +8300,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>199</v>
       </c>
@@ -8316,7 +8314,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>199</v>
       </c>
@@ -8330,7 +8328,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>199</v>
       </c>
@@ -8344,7 +8342,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>199</v>
       </c>
@@ -8358,7 +8356,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>199</v>
       </c>
@@ -8372,7 +8370,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>199</v>
       </c>
@@ -8386,7 +8384,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>199</v>
       </c>
@@ -8400,7 +8398,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>199</v>
       </c>
@@ -8414,7 +8412,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>199</v>
       </c>
@@ -8428,7 +8426,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>199</v>
       </c>
@@ -8442,7 +8440,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>199</v>
       </c>
@@ -8456,7 +8454,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>199</v>
       </c>
@@ -8470,7 +8468,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>199</v>
       </c>
@@ -8484,7 +8482,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>199</v>
       </c>
@@ -8498,7 +8496,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>199</v>
       </c>
@@ -8512,7 +8510,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>199</v>
       </c>
@@ -8526,7 +8524,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>199</v>
       </c>
@@ -8540,7 +8538,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>199</v>
       </c>
@@ -8554,7 +8552,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>199</v>
       </c>
@@ -8568,7 +8566,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>199</v>
       </c>
@@ -8582,7 +8580,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>199</v>
       </c>
@@ -8596,7 +8594,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>199</v>
       </c>
@@ -8610,7 +8608,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>199</v>
       </c>
@@ -8624,7 +8622,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>199</v>
       </c>
@@ -8638,7 +8636,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>199</v>
       </c>
@@ -8652,7 +8650,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>199</v>
       </c>
@@ -8666,7 +8664,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>199</v>
       </c>
@@ -8680,7 +8678,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>199</v>
       </c>
@@ -8694,7 +8692,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>199</v>
       </c>
@@ -8708,7 +8706,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>199</v>
       </c>
@@ -8722,7 +8720,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>199</v>
       </c>
@@ -8736,7 +8734,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>199</v>
       </c>
@@ -8750,7 +8748,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>199</v>
       </c>
@@ -8764,7 +8762,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>199</v>
       </c>
@@ -8778,7 +8776,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>199</v>
       </c>
@@ -8792,7 +8790,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>199</v>
       </c>
@@ -8806,7 +8804,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>199</v>
       </c>
@@ -8820,7 +8818,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>199</v>
       </c>
@@ -8834,7 +8832,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>199</v>
       </c>
@@ -8848,7 +8846,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>199</v>
       </c>
@@ -8862,7 +8860,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>199</v>
       </c>
@@ -8876,7 +8874,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>199</v>
       </c>
@@ -8890,7 +8888,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>199</v>
       </c>
@@ -8904,7 +8902,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>199</v>
       </c>
@@ -8918,7 +8916,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>199</v>
       </c>
@@ -8932,7 +8930,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>199</v>
       </c>
@@ -8946,7 +8944,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>199</v>
       </c>
@@ -8960,7 +8958,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>199</v>
       </c>
@@ -8974,7 +8972,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>199</v>
       </c>
@@ -8988,7 +8986,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>199</v>
       </c>
@@ -9002,7 +9000,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>199</v>
       </c>
@@ -9016,7 +9014,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>199</v>
       </c>
@@ -9030,7 +9028,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>199</v>
       </c>
@@ -9044,7 +9042,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>199</v>
       </c>
@@ -9058,7 +9056,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>199</v>
       </c>
@@ -9072,7 +9070,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>199</v>
       </c>
@@ -9086,7 +9084,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>199</v>
       </c>
@@ -9658,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>529</v>
       </c>
@@ -9687,7 +9685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>529</v>
       </c>
@@ -9716,7 +9714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>529</v>
       </c>
@@ -9745,7 +9743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>529</v>
       </c>
@@ -9774,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>529</v>
       </c>
@@ -9788,7 +9786,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>529</v>
       </c>
@@ -9817,7 +9815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>529</v>
       </c>
@@ -9849,7 +9847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>529</v>
       </c>
@@ -9878,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>529</v>
       </c>
@@ -9910,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>529</v>
       </c>
@@ -9939,7 +9937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>529</v>
       </c>
@@ -9971,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>529</v>
       </c>
@@ -10003,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>529</v>
       </c>
@@ -10032,7 +10030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>529</v>
       </c>
@@ -10061,7 +10059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>548</v>
       </c>
@@ -10090,7 +10088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>548</v>
       </c>
@@ -10119,7 +10117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>548</v>
       </c>
@@ -10151,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>548</v>
       </c>
@@ -10183,7 +10181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>548</v>
       </c>
@@ -10215,7 +10213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>548</v>
       </c>
@@ -10247,7 +10245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>548</v>
       </c>
@@ -10282,7 +10280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>564</v>
       </c>
@@ -10311,7 +10309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>564</v>
       </c>
@@ -10340,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>564</v>
       </c>
@@ -10369,7 +10367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>564</v>
       </c>
@@ -10398,7 +10396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>564</v>
       </c>
@@ -10412,7 +10410,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>564</v>
       </c>
@@ -10441,7 +10439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>564</v>
       </c>
@@ -10470,7 +10468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>564</v>
       </c>
@@ -10499,7 +10497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>564</v>
       </c>
@@ -10528,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>570</v>
       </c>
@@ -10560,7 +10558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>570</v>
       </c>
@@ -10592,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>570</v>
       </c>
@@ -10624,7 +10622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>570</v>
       </c>
@@ -10656,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>570</v>
       </c>
@@ -10688,7 +10686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>570</v>
       </c>
@@ -10723,7 +10721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>570</v>
       </c>
@@ -10758,7 +10756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>570</v>
       </c>
@@ -10793,7 +10791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>570</v>
       </c>
@@ -10825,7 +10823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>570</v>
       </c>
@@ -10857,7 +10855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>570</v>
       </c>
@@ -10889,7 +10887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>570</v>
       </c>
@@ -10921,7 +10919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>570</v>
       </c>
@@ -10953,7 +10951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>570</v>
       </c>
@@ -10985,7 +10983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>570</v>
       </c>
@@ -11017,7 +11015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>570</v>
       </c>
@@ -11049,7 +11047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>570</v>
       </c>
@@ -11081,7 +11079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>570</v>
       </c>
@@ -11116,7 +11114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>570</v>
       </c>
@@ -11148,7 +11146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>570</v>
       </c>
@@ -11183,7 +11181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>570</v>
       </c>
@@ -11215,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>570</v>
       </c>
@@ -11247,7 +11245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>570</v>
       </c>
@@ -11282,7 +11280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>570</v>
       </c>
@@ -11317,7 +11315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>570</v>
       </c>
@@ -11352,7 +11350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>570</v>
       </c>
@@ -11387,7 +11385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>570</v>
       </c>
@@ -11419,7 +11417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>570</v>
       </c>
@@ -11454,7 +11452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>570</v>
       </c>
@@ -11486,7 +11484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>570</v>
       </c>
@@ -11518,7 +11516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>570</v>
       </c>
@@ -11550,7 +11548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>570</v>
       </c>
@@ -11585,7 +11583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>570</v>
       </c>
@@ -11620,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>570</v>
       </c>

--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="11_5D050337D547D00E62355476585DCE3A87458E14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F816B01F-9C9D-4136-9E3A-475D3756E9D2}"/>
   <bookViews>
-    <workbookView xWindow="-36480" yWindow="-4440" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35085" yWindow="-270" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1286,6 +1286,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4451C641D253380E62355476585DCE3A874544FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_4451C641D253380E62355476585DCE3A874544FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3DF701C-8235-4E69-B247-A274DF43D669}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-3705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="394">
   <si>
     <t>file_name</t>
   </si>
@@ -1820,9 +1820,6 @@
       <c r="L7" t="s">
         <v>22</v>
       </c>
-      <c r="M7" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -2049,10 +2046,7 @@
         <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2134,7 +2128,7 @@
         <v>57</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -2421,7 +2415,7 @@
         <v>57</v>
       </c>
       <c r="N22" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2622,6 +2616,9 @@
       <c r="L27" t="s">
         <v>63</v>
       </c>
+      <c r="M27" t="s">
+        <v>57</v>
+      </c>
       <c r="N27" t="s">
         <v>83</v>
       </c>
@@ -2660,6 +2657,12 @@
       <c r="L28" t="s">
         <v>63</v>
       </c>
+      <c r="M28" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -3331,6 +3334,12 @@
       </c>
       <c r="L46" t="s">
         <v>22</v>
+      </c>
+      <c r="M46" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
+++ b/WP-2/Data_cleaning/ADNI_variables_statistics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifabfoundation-my.sharepoint.com/personal/chiara_pollicini_ifabfoundation_org/Documents/Documenti/Github/AIND/WP-2/Data_cleaning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_5B1506075248620F62355476585DCE3A8744B733" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6279E79C1467360E62355476585DCE3A8744AE35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48652264-5DC5-468F-9C8E-FAA47753F7D0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2699" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="511">
   <si>
     <t>file_name</t>
   </si>
@@ -1279,49 +1279,148 @@
     <t>UCSDVOL</t>
   </si>
   <si>
+    <t>sc, m06, m12, m24, m18, m36</t>
+  </si>
+  <si>
+    <t>QCPASS</t>
+  </si>
+  <si>
+    <t>1, 0</t>
+  </si>
+  <si>
+    <t>1.0, 0.0</t>
+  </si>
+  <si>
+    <t>BRAIN</t>
+  </si>
+  <si>
+    <t>1361820.0, 629016.0</t>
+  </si>
+  <si>
+    <t>EICV</t>
+  </si>
+  <si>
+    <t>1951440.0, 1059560.0</t>
+  </si>
+  <si>
+    <t>VENTRICLES</t>
+  </si>
+  <si>
+    <t>168830.0, 7552.46</t>
+  </si>
+  <si>
+    <t>LHIPPOC</t>
+  </si>
+  <si>
+    <t>5514.94, 1287.93</t>
+  </si>
+  <si>
+    <t>RHIPPOC</t>
+  </si>
+  <si>
+    <t>5750.4, 569.549</t>
+  </si>
+  <si>
+    <t>UPENN - ADNI/DIAN Study CSF Elecsys Results [ADNI1,GO,2]</t>
+  </si>
+  <si>
+    <t>UPENNBIOMK_ADNIDIAN_ES_2017</t>
+  </si>
+  <si>
     <t>None</t>
   </si>
   <si>
-    <t>sc, m06, m12, m24, m18, m36</t>
-  </si>
-  <si>
-    <t>QCPASS</t>
-  </si>
-  <si>
-    <t>1, 0</t>
-  </si>
-  <si>
-    <t>1.0, 0.0</t>
-  </si>
-  <si>
-    <t>BRAIN</t>
-  </si>
-  <si>
-    <t>1361820.0, 629016.0</t>
-  </si>
-  <si>
-    <t>EICV</t>
-  </si>
-  <si>
-    <t>1951440.0, 1059560.0</t>
-  </si>
-  <si>
-    <t>VENTRICLES</t>
-  </si>
-  <si>
-    <t>168830.0, 7552.46</t>
-  </si>
-  <si>
-    <t>LHIPPOC</t>
-  </si>
-  <si>
-    <t>5514.94, 1287.93</t>
-  </si>
-  <si>
-    <t>RHIPPOC</t>
-  </si>
-  <si>
-    <t>5750.4, 569.549</t>
+    <t>5285.0, 42.0</t>
+  </si>
+  <si>
+    <t>m60, m84, m108, m24, m36</t>
+  </si>
+  <si>
+    <t>2011-04-14, 2013-01-24, 2015-02-12, 2011-02-08, 2013-02-07</t>
+  </si>
+  <si>
+    <t>STUDY</t>
+  </si>
+  <si>
+    <t>ADNI</t>
+  </si>
+  <si>
+    <t>RUNDATE</t>
+  </si>
+  <si>
+    <t>2017-10-30, 2017-10-20, 2017-11-09, 2017-10-27, 2017-10-23</t>
+  </si>
+  <si>
+    <t>ABETA</t>
+  </si>
+  <si>
+    <t>pg/ml</t>
+  </si>
+  <si>
+    <t>2982.0, 238.0</t>
+  </si>
+  <si>
+    <t>AB40</t>
+  </si>
+  <si>
+    <t>37590.0, 5550.0</t>
+  </si>
+  <si>
+    <t>TAU</t>
+  </si>
+  <si>
+    <t>946.0, 110.0</t>
+  </si>
+  <si>
+    <t>PTAU</t>
+  </si>
+  <si>
+    <t>118.0, 8.0</t>
+  </si>
+  <si>
+    <t>A4240</t>
+  </si>
+  <si>
+    <t>0.1036, 0.0199</t>
+  </si>
+  <si>
+    <t>UPENN CSF Biomarkers Roche Elecsys [ADNI1,GO,2,3]</t>
+  </si>
+  <si>
+    <t>UPENNBIOMK_ROCHE_ELECSYS</t>
+  </si>
+  <si>
+    <t>7073.0, 3.0</t>
+  </si>
+  <si>
+    <t>bl, m12, m24, m48, m60</t>
+  </si>
+  <si>
+    <t>2005-09-12, 2006-09-13, 2005-11-22, 2006-11-28, 2005-09-07</t>
+  </si>
+  <si>
+    <t>ADNI1, ADNIGO, ADNI2, ADNI3</t>
+  </si>
+  <si>
+    <t>2016-12-14, 2017-01-09, 2016-11-22, 2017-01-06, 2016-11-17</t>
+  </si>
+  <si>
+    <t>ABETA40</t>
+  </si>
+  <si>
+    <t>37480.0, 841.0</t>
+  </si>
+  <si>
+    <t>ABETA42</t>
+  </si>
+  <si>
+    <t>4779.0, 203.0</t>
+  </si>
+  <si>
+    <t>1018.0, 80.08</t>
+  </si>
+  <si>
+    <t>108.5, 8.0</t>
   </si>
   <si>
     <t>The DIAN-ADNI Comparison Study</t>
@@ -1529,6 +1628,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1818,6 +1921,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N346"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="73.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -11193,9 +11300,6 @@
       <c r="F261" t="s">
         <v>23</v>
       </c>
-      <c r="G261" t="s">
-        <v>419</v>
-      </c>
       <c r="H261" t="s">
         <v>335</v>
       </c>
@@ -11229,9 +11333,6 @@
         <v>18</v>
       </c>
       <c r="G262" t="s">
-        <v>420</v>
-      </c>
-      <c r="H262" t="s">
         <v>419</v>
       </c>
       <c r="I262">
@@ -11266,9 +11367,6 @@
       <c r="G263" t="s">
         <v>337</v>
       </c>
-      <c r="H263" t="s">
-        <v>419</v>
-      </c>
       <c r="I263">
         <v>3128</v>
       </c>
@@ -11293,16 +11391,16 @@
         <v>159</v>
       </c>
       <c r="D264" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F264" t="s">
         <v>23</v>
       </c>
       <c r="G264" t="s">
+        <v>421</v>
+      </c>
+      <c r="H264" t="s">
         <v>422</v>
-      </c>
-      <c r="H264" t="s">
-        <v>423</v>
       </c>
       <c r="I264">
         <v>3128</v>
@@ -11328,7 +11426,7 @@
         <v>82</v>
       </c>
       <c r="D265" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E265" t="s">
         <v>254</v>
@@ -11336,11 +11434,8 @@
       <c r="F265" t="s">
         <v>23</v>
       </c>
-      <c r="G265" t="s">
-        <v>419</v>
-      </c>
       <c r="H265" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I265">
         <v>3128</v>
@@ -11372,7 +11467,7 @@
         <v>82</v>
       </c>
       <c r="D266" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E266" t="s">
         <v>254</v>
@@ -11380,11 +11475,8 @@
       <c r="F266" t="s">
         <v>23</v>
       </c>
-      <c r="G266" t="s">
-        <v>419</v>
-      </c>
       <c r="H266" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I266">
         <v>3128</v>
@@ -11416,7 +11508,7 @@
         <v>82</v>
       </c>
       <c r="D267" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E267" t="s">
         <v>254</v>
@@ -11424,11 +11516,8 @@
       <c r="F267" t="s">
         <v>35</v>
       </c>
-      <c r="G267" t="s">
-        <v>419</v>
-      </c>
       <c r="H267" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I267">
         <v>3128</v>
@@ -11460,7 +11549,7 @@
         <v>82</v>
       </c>
       <c r="D268" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E268" t="s">
         <v>254</v>
@@ -11468,11 +11557,8 @@
       <c r="F268" t="s">
         <v>35</v>
       </c>
-      <c r="G268" t="s">
-        <v>419</v>
-      </c>
       <c r="H268" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I268">
         <v>3128</v>
@@ -11504,7 +11590,7 @@
         <v>82</v>
       </c>
       <c r="D269" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E269" t="s">
         <v>254</v>
@@ -11512,11 +11598,8 @@
       <c r="F269" t="s">
         <v>35</v>
       </c>
-      <c r="G269" t="s">
-        <v>419</v>
-      </c>
       <c r="H269" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I269">
         <v>3128</v>
@@ -11537,12 +11620,758 @@
         <v>85</v>
       </c>
     </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>433</v>
+      </c>
+      <c r="B270" t="s">
+        <v>434</v>
+      </c>
+      <c r="C270" t="s">
+        <v>16</v>
+      </c>
+      <c r="D270" t="s">
+        <v>22</v>
+      </c>
+      <c r="F270" t="s">
+        <v>23</v>
+      </c>
+      <c r="G270" t="s">
+        <v>435</v>
+      </c>
+      <c r="H270" t="s">
+        <v>436</v>
+      </c>
+      <c r="I270">
+        <v>422</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270" t="s">
+        <v>144</v>
+      </c>
+      <c r="L270" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>433</v>
+      </c>
+      <c r="B271" t="s">
+        <v>434</v>
+      </c>
+      <c r="C271" t="s">
+        <v>106</v>
+      </c>
+      <c r="D271" t="s">
+        <v>107</v>
+      </c>
+      <c r="F271" t="s">
+        <v>18</v>
+      </c>
+      <c r="G271" t="s">
+        <v>437</v>
+      </c>
+      <c r="H271" t="s">
+        <v>435</v>
+      </c>
+      <c r="I271">
+        <v>422</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271" t="s">
+        <v>144</v>
+      </c>
+      <c r="L271" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>433</v>
+      </c>
+      <c r="B272" t="s">
+        <v>434</v>
+      </c>
+      <c r="C272" t="s">
+        <v>106</v>
+      </c>
+      <c r="D272" t="s">
+        <v>31</v>
+      </c>
+      <c r="F272" t="s">
+        <v>18</v>
+      </c>
+      <c r="G272" t="s">
+        <v>438</v>
+      </c>
+      <c r="H272" t="s">
+        <v>435</v>
+      </c>
+      <c r="I272">
+        <v>422</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272" t="s">
+        <v>144</v>
+      </c>
+      <c r="L272" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>433</v>
+      </c>
+      <c r="B273" t="s">
+        <v>434</v>
+      </c>
+      <c r="C273" t="s">
+        <v>25</v>
+      </c>
+      <c r="D273" t="s">
+        <v>439</v>
+      </c>
+      <c r="F273" t="s">
+        <v>18</v>
+      </c>
+      <c r="G273" t="s">
+        <v>440</v>
+      </c>
+      <c r="H273" t="s">
+        <v>435</v>
+      </c>
+      <c r="I273">
+        <v>422</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273" t="s">
+        <v>144</v>
+      </c>
+      <c r="L273" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>433</v>
+      </c>
+      <c r="B274" t="s">
+        <v>434</v>
+      </c>
+      <c r="C274" t="s">
+        <v>106</v>
+      </c>
+      <c r="D274" t="s">
+        <v>441</v>
+      </c>
+      <c r="F274" t="s">
+        <v>18</v>
+      </c>
+      <c r="G274" t="s">
+        <v>442</v>
+      </c>
+      <c r="H274" t="s">
+        <v>435</v>
+      </c>
+      <c r="I274">
+        <v>422</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274" t="s">
+        <v>144</v>
+      </c>
+      <c r="L274" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>433</v>
+      </c>
+      <c r="B275" t="s">
+        <v>434</v>
+      </c>
+      <c r="C275" t="s">
+        <v>56</v>
+      </c>
+      <c r="D275" t="s">
+        <v>443</v>
+      </c>
+      <c r="E275" t="s">
+        <v>444</v>
+      </c>
+      <c r="F275" t="s">
+        <v>23</v>
+      </c>
+      <c r="G275" t="s">
+        <v>435</v>
+      </c>
+      <c r="H275" t="s">
+        <v>445</v>
+      </c>
+      <c r="I275">
+        <v>422</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275" t="s">
+        <v>144</v>
+      </c>
+      <c r="L275" t="s">
+        <v>21</v>
+      </c>
+      <c r="M275" t="s">
+        <v>61</v>
+      </c>
+      <c r="N275" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>433</v>
+      </c>
+      <c r="B276" t="s">
+        <v>434</v>
+      </c>
+      <c r="C276" t="s">
+        <v>56</v>
+      </c>
+      <c r="D276" t="s">
+        <v>446</v>
+      </c>
+      <c r="E276" t="s">
+        <v>444</v>
+      </c>
+      <c r="F276" t="s">
+        <v>23</v>
+      </c>
+      <c r="G276" t="s">
+        <v>435</v>
+      </c>
+      <c r="H276" t="s">
+        <v>447</v>
+      </c>
+      <c r="I276">
+        <v>422</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276" t="s">
+        <v>144</v>
+      </c>
+      <c r="L276" t="s">
+        <v>21</v>
+      </c>
+      <c r="M276" t="s">
+        <v>61</v>
+      </c>
+      <c r="N276" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>433</v>
+      </c>
+      <c r="B277" t="s">
+        <v>434</v>
+      </c>
+      <c r="C277" t="s">
+        <v>120</v>
+      </c>
+      <c r="D277" t="s">
+        <v>448</v>
+      </c>
+      <c r="E277" t="s">
+        <v>444</v>
+      </c>
+      <c r="F277" t="s">
+        <v>23</v>
+      </c>
+      <c r="G277" t="s">
+        <v>435</v>
+      </c>
+      <c r="H277" t="s">
+        <v>449</v>
+      </c>
+      <c r="I277">
+        <v>422</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277" t="s">
+        <v>144</v>
+      </c>
+      <c r="L277" t="s">
+        <v>21</v>
+      </c>
+      <c r="M277" t="s">
+        <v>61</v>
+      </c>
+      <c r="N277" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>433</v>
+      </c>
+      <c r="B278" t="s">
+        <v>434</v>
+      </c>
+      <c r="C278" t="s">
+        <v>120</v>
+      </c>
+      <c r="D278" t="s">
+        <v>450</v>
+      </c>
+      <c r="E278" t="s">
+        <v>444</v>
+      </c>
+      <c r="F278" t="s">
+        <v>35</v>
+      </c>
+      <c r="G278" t="s">
+        <v>435</v>
+      </c>
+      <c r="H278" t="s">
+        <v>451</v>
+      </c>
+      <c r="I278">
+        <v>421</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278" t="s">
+        <v>144</v>
+      </c>
+      <c r="L278" t="s">
+        <v>21</v>
+      </c>
+      <c r="M278" t="s">
+        <v>61</v>
+      </c>
+      <c r="N278" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>433</v>
+      </c>
+      <c r="B279" t="s">
+        <v>434</v>
+      </c>
+      <c r="C279" t="s">
+        <v>56</v>
+      </c>
+      <c r="D279" t="s">
+        <v>452</v>
+      </c>
+      <c r="E279" t="s">
+        <v>444</v>
+      </c>
+      <c r="F279" t="s">
+        <v>35</v>
+      </c>
+      <c r="G279" t="s">
+        <v>435</v>
+      </c>
+      <c r="H279" t="s">
+        <v>453</v>
+      </c>
+      <c r="I279">
+        <v>422</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279" t="s">
+        <v>144</v>
+      </c>
+      <c r="L279" t="s">
+        <v>21</v>
+      </c>
+      <c r="M279" t="s">
+        <v>61</v>
+      </c>
+      <c r="N279" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>454</v>
+      </c>
+      <c r="B280" t="s">
+        <v>455</v>
+      </c>
+      <c r="C280" t="s">
+        <v>16</v>
+      </c>
+      <c r="D280" t="s">
+        <v>22</v>
+      </c>
+      <c r="F280" t="s">
+        <v>23</v>
+      </c>
+      <c r="G280" t="s">
+        <v>435</v>
+      </c>
+      <c r="H280" t="s">
+        <v>456</v>
+      </c>
+      <c r="I280">
+        <v>3174</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280" t="s">
+        <v>20</v>
+      </c>
+      <c r="L280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>454</v>
+      </c>
+      <c r="B281" t="s">
+        <v>455</v>
+      </c>
+      <c r="C281" t="s">
+        <v>106</v>
+      </c>
+      <c r="D281" t="s">
+        <v>107</v>
+      </c>
+      <c r="F281" t="s">
+        <v>18</v>
+      </c>
+      <c r="G281" t="s">
+        <v>457</v>
+      </c>
+      <c r="H281" t="s">
+        <v>435</v>
+      </c>
+      <c r="I281">
+        <v>3174</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281" t="s">
+        <v>20</v>
+      </c>
+      <c r="L281" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>454</v>
+      </c>
+      <c r="B282" t="s">
+        <v>455</v>
+      </c>
+      <c r="C282" t="s">
+        <v>106</v>
+      </c>
+      <c r="D282" t="s">
+        <v>31</v>
+      </c>
+      <c r="F282" t="s">
+        <v>18</v>
+      </c>
+      <c r="G282" t="s">
+        <v>458</v>
+      </c>
+      <c r="H282" t="s">
+        <v>435</v>
+      </c>
+      <c r="I282">
+        <v>3174</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282" t="s">
+        <v>20</v>
+      </c>
+      <c r="L282" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>454</v>
+      </c>
+      <c r="B283" t="s">
+        <v>455</v>
+      </c>
+      <c r="C283" t="s">
+        <v>25</v>
+      </c>
+      <c r="D283" t="s">
+        <v>104</v>
+      </c>
+      <c r="F283" t="s">
+        <v>18</v>
+      </c>
+      <c r="G283" t="s">
+        <v>459</v>
+      </c>
+      <c r="H283" t="s">
+        <v>435</v>
+      </c>
+      <c r="I283">
+        <v>3174</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283" t="s">
+        <v>20</v>
+      </c>
+      <c r="L283" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>454</v>
+      </c>
+      <c r="B284" t="s">
+        <v>455</v>
+      </c>
+      <c r="C284" t="s">
+        <v>106</v>
+      </c>
+      <c r="D284" t="s">
+        <v>441</v>
+      </c>
+      <c r="F284" t="s">
+        <v>18</v>
+      </c>
+      <c r="G284" t="s">
+        <v>460</v>
+      </c>
+      <c r="H284" t="s">
+        <v>435</v>
+      </c>
+      <c r="I284">
+        <v>3174</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284" t="s">
+        <v>20</v>
+      </c>
+      <c r="L284" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>454</v>
+      </c>
+      <c r="B285" t="s">
+        <v>455</v>
+      </c>
+      <c r="C285" t="s">
+        <v>56</v>
+      </c>
+      <c r="D285" t="s">
+        <v>461</v>
+      </c>
+      <c r="E285" t="s">
+        <v>444</v>
+      </c>
+      <c r="F285" t="s">
+        <v>35</v>
+      </c>
+      <c r="G285" t="s">
+        <v>435</v>
+      </c>
+      <c r="H285" t="s">
+        <v>462</v>
+      </c>
+      <c r="I285">
+        <v>934</v>
+      </c>
+      <c r="J285">
+        <v>2240</v>
+      </c>
+      <c r="K285" t="s">
+        <v>20</v>
+      </c>
+      <c r="L285" t="s">
+        <v>60</v>
+      </c>
+      <c r="M285" t="s">
+        <v>61</v>
+      </c>
+      <c r="N285" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>454</v>
+      </c>
+      <c r="B286" t="s">
+        <v>455</v>
+      </c>
+      <c r="C286" t="s">
+        <v>56</v>
+      </c>
+      <c r="D286" t="s">
+        <v>463</v>
+      </c>
+      <c r="E286" t="s">
+        <v>444</v>
+      </c>
+      <c r="F286" t="s">
+        <v>35</v>
+      </c>
+      <c r="G286" t="s">
+        <v>435</v>
+      </c>
+      <c r="H286" t="s">
+        <v>464</v>
+      </c>
+      <c r="I286">
+        <v>3167</v>
+      </c>
+      <c r="J286">
+        <v>7</v>
+      </c>
+      <c r="K286" t="s">
+        <v>20</v>
+      </c>
+      <c r="L286" t="s">
+        <v>21</v>
+      </c>
+      <c r="M286" t="s">
+        <v>61</v>
+      </c>
+      <c r="N286" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>454</v>
+      </c>
+      <c r="B287" t="s">
+        <v>455</v>
+      </c>
+      <c r="C287" t="s">
+        <v>120</v>
+      </c>
+      <c r="D287" t="s">
+        <v>448</v>
+      </c>
+      <c r="E287" t="s">
+        <v>444</v>
+      </c>
+      <c r="F287" t="s">
+        <v>35</v>
+      </c>
+      <c r="G287" t="s">
+        <v>435</v>
+      </c>
+      <c r="H287" t="s">
+        <v>465</v>
+      </c>
+      <c r="I287">
+        <v>3159</v>
+      </c>
+      <c r="J287">
+        <v>15</v>
+      </c>
+      <c r="K287" t="s">
+        <v>20</v>
+      </c>
+      <c r="L287" t="s">
+        <v>21</v>
+      </c>
+      <c r="M287" t="s">
+        <v>61</v>
+      </c>
+      <c r="N287" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>454</v>
+      </c>
+      <c r="B288" t="s">
+        <v>455</v>
+      </c>
+      <c r="C288" t="s">
+        <v>120</v>
+      </c>
+      <c r="D288" t="s">
+        <v>450</v>
+      </c>
+      <c r="E288" t="s">
+        <v>444</v>
+      </c>
+      <c r="F288" t="s">
+        <v>35</v>
+      </c>
+      <c r="G288" t="s">
+        <v>435</v>
+      </c>
+      <c r="H288" t="s">
+        <v>466</v>
+      </c>
+      <c r="I288">
+        <v>3147</v>
+      </c>
+      <c r="J288">
+        <v>27</v>
+      </c>
+      <c r="K288" t="s">
+        <v>20</v>
+      </c>
+      <c r="L288" t="s">
+        <v>21</v>
+      </c>
+      <c r="M288" t="s">
+        <v>61</v>
+      </c>
+      <c r="N288" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B303" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C303" t="s">
         <v>16</v>
@@ -11553,10 +12382,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B304" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C304" t="s">
         <v>28</v>
@@ -11567,593 +12396,594 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B305" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C305" t="s">
         <v>33</v>
       </c>
       <c r="D305" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B306" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C306" t="s">
         <v>66</v>
       </c>
       <c r="D306" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B307" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C307" t="s">
         <v>66</v>
       </c>
       <c r="D307" t="s">
-        <v>438</v>
+        <v>471</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B308" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C308" t="s">
         <v>66</v>
       </c>
       <c r="D308" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B309" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C309" t="s">
         <v>159</v>
       </c>
       <c r="D309" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B310" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C310" t="s">
         <v>106</v>
       </c>
       <c r="D310" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B311" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C311" t="s">
         <v>66</v>
       </c>
       <c r="D311" t="s">
-        <v>442</v>
+        <v>475</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B312" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C312" t="s">
         <v>66</v>
       </c>
       <c r="D312" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B313" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C313" t="s">
         <v>159</v>
       </c>
       <c r="D313" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B314" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C314" t="s">
         <v>56</v>
       </c>
       <c r="D314" t="s">
-        <v>445</v>
+        <v>478</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B315" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C315" t="s">
         <v>56</v>
       </c>
       <c r="D315" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B316" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C316" t="s">
         <v>56</v>
       </c>
       <c r="D316" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B317" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C317" t="s">
         <v>120</v>
       </c>
       <c r="D317" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B318" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C318" t="s">
         <v>120</v>
       </c>
       <c r="D318" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B319" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C319" t="s">
         <v>52</v>
       </c>
       <c r="D319" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B320" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C320" t="s">
         <v>66</v>
       </c>
       <c r="D320" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B321" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C321" t="s">
         <v>75</v>
       </c>
       <c r="D321" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B322" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C322" t="s">
         <v>33</v>
       </c>
       <c r="D322" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B323" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C323" t="s">
         <v>37</v>
       </c>
       <c r="D323" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B324" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C324" t="s">
         <v>106</v>
       </c>
       <c r="D324" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B325" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C325" t="s">
         <v>49</v>
       </c>
       <c r="D325" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B326" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C326" t="s">
         <v>66</v>
       </c>
       <c r="D326" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B327" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C327" t="s">
         <v>66</v>
       </c>
       <c r="D327" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B328" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C328" t="s">
         <v>106</v>
       </c>
       <c r="D328" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B329" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C329" t="s">
         <v>106</v>
       </c>
       <c r="D329" t="s">
-        <v>460</v>
+        <v>493</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B330" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C330" t="s">
         <v>82</v>
       </c>
       <c r="D330" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B331" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C331" t="s">
         <v>82</v>
       </c>
       <c r="D331" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B332" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C332" t="s">
         <v>82</v>
       </c>
       <c r="D332" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B333" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C333" t="s">
         <v>82</v>
       </c>
       <c r="D333" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B334" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C334" t="s">
         <v>66</v>
       </c>
       <c r="D334" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B335" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C335" t="s">
         <v>66</v>
       </c>
       <c r="D335" t="s">
-        <v>466</v>
+        <v>499</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B336" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C336" t="s">
         <v>106</v>
       </c>
       <c r="D336" t="s">
-        <v>467</v>
+        <v>500</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B337" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C337" t="s">
         <v>106</v>
       </c>
       <c r="D337" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B338" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C338" t="s">
         <v>159</v>
       </c>
       <c r="D338" t="s">
-        <v>469</v>
+        <v>502</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B339" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C339" t="s">
         <v>56</v>
       </c>
       <c r="D339" t="s">
-        <v>470</v>
+        <v>503</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B340" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C340" t="s">
         <v>56</v>
       </c>
       <c r="D340" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B341" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C341" t="s">
         <v>56</v>
       </c>
       <c r="D341" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B342" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C342" t="s">
         <v>56</v>
       </c>
       <c r="D342" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B343" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C343" t="s">
         <v>56</v>
       </c>
       <c r="D343" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B344" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C344" t="s">
         <v>44</v>
       </c>
       <c r="D344" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B345" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C345" t="s">
         <v>33</v>
       </c>
       <c r="D345" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="B346" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="C346" t="s">
         <v>28</v>
       </c>
       <c r="D346" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>